--- a/examples/wangetal2018/out/ResultFiles/AC_0.5_a.xlsx
+++ b/examples/wangetal2018/out/ResultFiles/AC_0.5_a.xlsx
@@ -14,17 +14,18 @@
     <sheet name="Compressor design" sheetId="5" r:id="rId5"/>
     <sheet name="Pressure profile" sheetId="6" r:id="rId6"/>
     <sheet name="Demand error" sheetId="7" r:id="rId7"/>
+    <sheet name="ProFAST" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="379">
   <si>
     <t xml:space="preserve">
 ---------DISCLAIMER---------
-AS NOTED IN THE LICENSE, ALLIANCE FOR SUSTAINABLE ENERGY, LLC: (i) DISCLAIMS ANY WARRANTIES, EXPRESS OR IMPLIED, INCLUDING BUT NOT LIMITED TO ANY IMPLIED WARRANTIES OF MERCHANTABILITY, FITNESS FOR A PARTICULAR PURPOSE, TITLE OR NON-INFRINGEMENT, AND (ii) DOES NOT ASSUME ANY LEGAL LIABILITY OR RESPONSIBILITY FOR THE ACCURACY, COMPLETENESS, OR USEFULNESS OF SOFTWARE OR ITS OUTPUTS. ANY RELIANCE BY THE USER ON THE SOFTWARE IS DONE AT THE USER’S OWN RISK.
+AS NOTED IN THE LICENSE, ALLIANCE FOR ENERGY INNOVATION, LLC: (i) DISCLAIMS ANY WARRANTIES, EXPRESS OR IMPLIED, INCLUDING BUT NOT LIMITED TO ANY IMPLIED WARRANTIES OF MERCHANTABILITY, FITNESS FOR A PARTICULAR PURPOSE, TITLE OR NON-INFRINGEMENT, AND (ii) DOES NOT ASSUME ANY LEGAL LIABILITY OR RESPONSIBILITY FOR THE ACCURACY, COMPLETENESS, OR USEFULNESS OF SOFTWARE OR ITS OUTPUTS. ANY RELIANCE BY THE USER ON THE SOFTWARE IS DONE AT THE USER’S OWN RISK.
 BlendPATH was developed to provide the user with economic analytical capabilities to evaluate potential natural gas transmission pipeline modifications for accommodating hydrogen blending or pure hydrogen streams and to assess the potential associated economic impacts. This model is intended for use during the early stages of pipeline repurposing concept evaluation, which is defined here as the initial project phase when the developer has already gathered the relevant pipeline material design and operation data but has not yet conducted the detailed pipeline materials testing, as specified in ASME B31.12, or performed the in-line inspections that qualify a given pipeline section for hydrogen or hydrogen blending service. Despite BlendPATH using ASME B31.12 to assess existing natural gas transmission pipelines and establish potential pipeline modifications for a natural gas transmission pipeline network to meet ASME B31.12 design requirements, BlendPATH does not qualify the examined pipeline network or modifications thereof for pure hydrogen or hydrogen blending. Pipeline owners and operators must conduct additional evaluations as specified in ASME B31.12 and other relevant code and regulations, independent of BlendPATH application, to qualify actual natural gas transmission pipelines for operation with hydrogen. Failure to do so may result in pipeline fatigue and/or rupture. It is the sole responsibility of the pipeline owner and operator to ensure that their pipeline qualifies for the ASME B31.12 design option that they choose, and any other relevant code and regulations, and that any defects present in the pipeline are acceptable at the operating pressure chosen.
 ----------------------------
 </t>
@@ -39,12 +40,21 @@
     <t>Network name</t>
   </si>
   <si>
+    <t>examples/wangetal2018</t>
+  </si>
+  <si>
     <t>Save directory</t>
   </si>
   <si>
+    <t>out</t>
+  </si>
+  <si>
     <t>Design option - original</t>
   </si>
   <si>
+    <t>a</t>
+  </si>
+  <si>
     <t>Location class</t>
   </si>
   <si>
@@ -57,6 +67,9 @@
     <t>Compression ratio</t>
   </si>
   <si>
+    <t>[1.2, 1.4, 1.6, 1.8, 2.0]</t>
+  </si>
+  <si>
     <t>Blending ratio</t>
   </si>
   <si>
@@ -75,18 +88,27 @@
     <t>Region</t>
   </si>
   <si>
+    <t>GP</t>
+  </si>
+  <si>
     <t>Modification method</t>
   </si>
   <si>
+    <t>ac</t>
+  </si>
+  <si>
     <t>Modification design option</t>
   </si>
   <si>
-    <t>Verbose</t>
+    <t>b</t>
   </si>
   <si>
     <t>Equation of state</t>
   </si>
   <si>
+    <t>rk</t>
+  </si>
+  <si>
     <t>Inline inspection inspection interval</t>
   </si>
   <si>
@@ -111,28 +133,40 @@
     <t>New electric compressor driver efficiency</t>
   </si>
   <si>
-    <t>examples/wangetal2018</t>
-  </si>
-  <si>
-    <t>out</t>
-  </si>
-  <si>
-    <t>a</t>
-  </si>
-  <si>
-    <t>[1.2, 1.4, 1.6, 1.8, 2.0]</t>
-  </si>
-  <si>
-    <t>GP</t>
-  </si>
-  <si>
-    <t>ac</t>
-  </si>
-  <si>
-    <t>b</t>
-  </si>
-  <si>
-    <t>rk</t>
+    <t>Pipe price markup</t>
+  </si>
+  <si>
+    <t>Compressor price markup</t>
+  </si>
+  <si>
+    <t>Financial overrides</t>
+  </si>
+  <si>
+    <t>{}</t>
+  </si>
+  <si>
+    <t>Filename suffix</t>
+  </si>
+  <si>
+    <t>Thermodynamic curvefits enabled</t>
+  </si>
+  <si>
+    <t>Composition tracking enabled</t>
+  </si>
+  <si>
+    <t>Scenario type</t>
+  </si>
+  <si>
+    <t>transmission</t>
+  </si>
+  <si>
+    <t>Polymer cost type</t>
+  </si>
+  <si>
+    <t>socal</t>
+  </si>
+  <si>
+    <t>Max velocity allowed in distribution networks</t>
   </si>
   <si>
     <t>Parameter</t>
@@ -144,6 +178,9 @@
     <t>LCOT: Levelized cost of transport</t>
   </si>
   <si>
+    <t>$/MMBTU</t>
+  </si>
+  <si>
     <t>LCOT: New pipe CapEx</t>
   </si>
   <si>
@@ -180,6 +217,12 @@
     <t>LCOT: Supply commpressor fuel</t>
   </si>
   <si>
+    <t>LCOT: Meter set assembly</t>
+  </si>
+  <si>
+    <t>LCOT: Gas pressure regulation and metering station</t>
+  </si>
+  <si>
     <t>LCOT: Fixed O&amp;M</t>
   </si>
   <si>
@@ -192,6 +235,9 @@
     <t>Hydrogen injection price</t>
   </si>
   <si>
+    <t>$/kg</t>
+  </si>
+  <si>
     <t>Natural gas price</t>
   </si>
   <si>
@@ -201,27 +247,48 @@
     <t>Pipeline capacity (daily)</t>
   </si>
   <si>
+    <t>MMBTU/day</t>
+  </si>
+  <si>
     <t>Pipeline capacity (hour)</t>
   </si>
   <si>
+    <t>MMBTU/hr</t>
+  </si>
+  <si>
     <t>Added pipeline</t>
   </si>
   <si>
+    <t>km</t>
+  </si>
+  <si>
+    <t>mi</t>
+  </si>
+  <si>
     <t>Added compressor stations</t>
   </si>
   <si>
     <t>Added compressor capacity</t>
   </si>
   <si>
+    <t>hp</t>
+  </si>
+  <si>
     <t>Compressor fuel usage</t>
   </si>
   <si>
     <t>Compressor fuel usage (electric)</t>
   </si>
   <si>
+    <t>kW</t>
+  </si>
+  <si>
     <t>New pipe</t>
   </si>
   <si>
+    <t>$</t>
+  </si>
+  <si>
     <t>New compressor stations</t>
   </si>
   <si>
@@ -234,39 +301,30 @@
     <t>Valve modifications</t>
   </si>
   <si>
+    <t>Meter set assembly</t>
+  </si>
+  <si>
+    <t>Gas pressure regulating metering station</t>
+  </si>
+  <si>
     <t>Hydrogen energy ratio</t>
   </si>
   <si>
-    <t>$/MMBTU</t>
-  </si>
-  <si>
-    <t>$/kg</t>
-  </si>
-  <si>
-    <t>MMBTU/day</t>
-  </si>
-  <si>
-    <t>MMBTU/hr</t>
-  </si>
-  <si>
-    <t>km</t>
-  </si>
-  <si>
-    <t>mi</t>
-  </si>
-  <si>
-    <t>hp</t>
-  </si>
-  <si>
-    <t>kW</t>
-  </si>
-  <si>
-    <t>$</t>
-  </si>
-  <si>
     <t>%</t>
   </si>
   <si>
+    <t>Emissions intensity (total)</t>
+  </si>
+  <si>
+    <t>kgCO2e/MMBTU</t>
+  </si>
+  <si>
+    <t>Total emissions (annual)</t>
+  </si>
+  <si>
+    <t>MMTCO2e/yr</t>
+  </si>
+  <si>
     <t>Breakdown of original pipe by diameter, schedule and grade</t>
   </si>
   <si>
@@ -282,6 +340,9 @@
     <t>Schedule</t>
   </si>
   <si>
+    <t>Polymer</t>
+  </si>
+  <si>
     <t>X60</t>
   </si>
   <si>
@@ -342,12 +403,6 @@
     <t>C_0_2</t>
   </si>
   <si>
-    <t>C_0_3</t>
-  </si>
-  <si>
-    <t>C_0_4</t>
-  </si>
-  <si>
     <t>CS1</t>
   </si>
   <si>
@@ -372,15 +427,6 @@
     <t>C_1_6</t>
   </si>
   <si>
-    <t>C_1_7</t>
-  </si>
-  <si>
-    <t>C_1_8</t>
-  </si>
-  <si>
-    <t>C_1_9</t>
-  </si>
-  <si>
     <t>CS2</t>
   </si>
   <si>
@@ -453,348 +499,303 @@
     <t>Erosional velocity (m/s)</t>
   </si>
   <si>
-    <t>PI01_0_pre_C_0_0</t>
-  </si>
-  <si>
-    <t>PI01_0_remaining</t>
-  </si>
-  <si>
-    <t>PI01_1_pre_C_0_1</t>
+    <t>PI01_0</t>
+  </si>
+  <si>
+    <t>N01</t>
+  </si>
+  <si>
+    <t>N01_0</t>
+  </si>
+  <si>
+    <t>Existing</t>
+  </si>
+  <si>
+    <t>PI01_1_pre_C_0_0</t>
+  </si>
+  <si>
+    <t>N_pre_C_0_0</t>
   </si>
   <si>
     <t>PI01_1_remaining</t>
   </si>
   <si>
-    <t>PI01_pre_C_0_2</t>
+    <t>N_post_C_0_0</t>
+  </si>
+  <si>
+    <t>N01_1</t>
+  </si>
+  <si>
+    <t>PI01_pre_C_0_1</t>
+  </si>
+  <si>
+    <t>N_pre_C_0_1</t>
   </si>
   <si>
     <t>PI01_remaining</t>
   </si>
   <si>
-    <t>PI02_0_pre_C_0_3</t>
+    <t>N_post_C_0_1</t>
+  </si>
+  <si>
+    <t>N02</t>
+  </si>
+  <si>
+    <t>PI02_0_pre_C_0_2</t>
+  </si>
+  <si>
+    <t>N_pre_C_0_2</t>
   </si>
   <si>
     <t>PI02_0_remaining</t>
   </si>
   <si>
-    <t>PI02_pre_C_0_4</t>
-  </si>
-  <si>
-    <t>PI02_remaining</t>
-  </si>
-  <si>
-    <t>PI03_0_pre_C_1_0</t>
-  </si>
-  <si>
-    <t>PI03_0_remaining</t>
-  </si>
-  <si>
-    <t>PI03_pre_C_1_1</t>
+    <t>N_post_C_0_2</t>
+  </si>
+  <si>
+    <t>N02_0</t>
+  </si>
+  <si>
+    <t>PI02</t>
+  </si>
+  <si>
+    <t>N03</t>
+  </si>
+  <si>
+    <t>PI03_0</t>
+  </si>
+  <si>
+    <t>N03_C</t>
+  </si>
+  <si>
+    <t>N03_C_0</t>
+  </si>
+  <si>
+    <t>PI03_pre_C_1_0</t>
+  </si>
+  <si>
+    <t>N_pre_C_1_0</t>
   </si>
   <si>
     <t>PI03_remaining</t>
   </si>
   <si>
-    <t>PI04_0_pre_C_1_2</t>
-  </si>
-  <si>
-    <t>PI04_0_pre_C_1_3</t>
+    <t>N_post_C_1_0</t>
+  </si>
+  <si>
+    <t>N04</t>
+  </si>
+  <si>
+    <t>PI04_0_pre_C_1_1</t>
+  </si>
+  <si>
+    <t>N_pre_C_1_1</t>
   </si>
   <si>
     <t>PI04_0_remaining</t>
   </si>
   <si>
-    <t>PI04_1_pre_C_1_4</t>
+    <t>N_post_C_1_1</t>
+  </si>
+  <si>
+    <t>N04_0</t>
+  </si>
+  <si>
+    <t>PI04_1_pre_C_1_2</t>
+  </si>
+  <si>
+    <t>N_pre_C_1_2</t>
   </si>
   <si>
     <t>PI04_1_remaining</t>
   </si>
   <si>
-    <t>PI04_pre_C_1_5</t>
+    <t>N_post_C_1_2</t>
+  </si>
+  <si>
+    <t>N04_1</t>
+  </si>
+  <si>
+    <t>PI04_pre_C_1_3</t>
+  </si>
+  <si>
+    <t>N_pre_C_1_3</t>
   </si>
   <si>
     <t>PI04_remaining</t>
   </si>
   <si>
-    <t>PI05_0_pre_C_1_6</t>
-  </si>
-  <si>
-    <t>PI05_0_pre_C_1_7</t>
+    <t>N_post_C_1_3</t>
+  </si>
+  <si>
+    <t>N05</t>
+  </si>
+  <si>
+    <t>PI05_0_pre_C_1_4</t>
+  </si>
+  <si>
+    <t>N_pre_C_1_4</t>
   </si>
   <si>
     <t>PI05_0_remaining</t>
   </si>
   <si>
-    <t>PI05_1_pre_C_1_8</t>
+    <t>N_post_C_1_4</t>
+  </si>
+  <si>
+    <t>N05_0</t>
+  </si>
+  <si>
+    <t>PI05_1_pre_C_1_5</t>
+  </si>
+  <si>
+    <t>N_pre_C_1_5</t>
   </si>
   <si>
     <t>PI05_1_remaining</t>
   </si>
   <si>
-    <t>PI05_pre_C_1_9</t>
+    <t>N_post_C_1_5</t>
+  </si>
+  <si>
+    <t>N05_1</t>
+  </si>
+  <si>
+    <t>PI05_pre_C_1_6</t>
+  </si>
+  <si>
+    <t>N_pre_C_1_6</t>
   </si>
   <si>
     <t>PI05_remaining</t>
   </si>
   <si>
+    <t>N_post_C_1_6</t>
+  </si>
+  <si>
+    <t>N06</t>
+  </si>
+  <si>
     <t>PI06_0</t>
   </si>
   <si>
+    <t>N06_C</t>
+  </si>
+  <si>
+    <t>N06_C_0</t>
+  </si>
+  <si>
     <t>PI06_1_pre_C_2_0</t>
   </si>
   <si>
+    <t>N_pre_C_2_0</t>
+  </si>
+  <si>
     <t>PI06_1_remaining</t>
   </si>
   <si>
+    <t>N_post_C_2_0</t>
+  </si>
+  <si>
+    <t>N06_C_1</t>
+  </si>
+  <si>
     <t>PI06</t>
   </si>
   <si>
+    <t>N_pre_C_2_1</t>
+  </si>
+  <si>
     <t>PI07_0_remaining</t>
   </si>
   <si>
+    <t>N07</t>
+  </si>
+  <si>
+    <t>N07_0</t>
+  </si>
+  <si>
     <t>PI07_1_pre_C_2_2</t>
   </si>
   <si>
+    <t>N_pre_C_2_2</t>
+  </si>
+  <si>
     <t>PI07_1_remaining</t>
   </si>
   <si>
+    <t>N_post_C_2_2</t>
+  </si>
+  <si>
+    <t>N07_1</t>
+  </si>
+  <si>
     <t>PI07</t>
   </si>
   <si>
+    <t>N08</t>
+  </si>
+  <si>
     <t>PI08_0</t>
   </si>
   <si>
+    <t>N08_C</t>
+  </si>
+  <si>
+    <t>N08_C_0</t>
+  </si>
+  <si>
     <t>PI08_1_pre_C_3_0</t>
   </si>
   <si>
+    <t>N_pre_C_3_0</t>
+  </si>
+  <si>
     <t>PI08_1_remaining</t>
   </si>
   <si>
+    <t>N_post_C_3_0</t>
+  </si>
+  <si>
+    <t>N08_C_1</t>
+  </si>
+  <si>
     <t>PI08</t>
   </si>
   <si>
+    <t>N_pre_C_3_1</t>
+  </si>
+  <si>
     <t>PI09_0_remaining</t>
   </si>
   <si>
+    <t>N09</t>
+  </si>
+  <si>
+    <t>N09_0</t>
+  </si>
+  <si>
     <t>PI09_1_pre_C_3_2</t>
   </si>
   <si>
+    <t>N_pre_C_3_2</t>
+  </si>
+  <si>
     <t>PI09_1_remaining</t>
   </si>
   <si>
+    <t>N_post_C_3_2</t>
+  </si>
+  <si>
+    <t>N09_1</t>
+  </si>
+  <si>
     <t>PI09</t>
   </si>
   <si>
-    <t>N01</t>
-  </si>
-  <si>
-    <t>N_post_C_0_0</t>
-  </si>
-  <si>
-    <t>N01_0</t>
-  </si>
-  <si>
-    <t>N_post_C_0_1</t>
-  </si>
-  <si>
-    <t>N01_1</t>
-  </si>
-  <si>
-    <t>N_post_C_0_2</t>
-  </si>
-  <si>
-    <t>N02</t>
-  </si>
-  <si>
-    <t>N_post_C_0_3</t>
-  </si>
-  <si>
-    <t>N02_0</t>
-  </si>
-  <si>
-    <t>N_post_C_0_4</t>
-  </si>
-  <si>
-    <t>N03_C</t>
-  </si>
-  <si>
-    <t>N_post_C_1_0</t>
-  </si>
-  <si>
-    <t>N03_C_0</t>
-  </si>
-  <si>
-    <t>N_post_C_1_1</t>
-  </si>
-  <si>
-    <t>N04</t>
-  </si>
-  <si>
-    <t>N_post_C_1_2</t>
-  </si>
-  <si>
-    <t>N_post_C_1_3</t>
-  </si>
-  <si>
-    <t>N04_0</t>
-  </si>
-  <si>
-    <t>N_post_C_1_4</t>
-  </si>
-  <si>
-    <t>N04_1</t>
-  </si>
-  <si>
-    <t>N_post_C_1_5</t>
-  </si>
-  <si>
-    <t>N05</t>
-  </si>
-  <si>
-    <t>N_post_C_1_6</t>
-  </si>
-  <si>
-    <t>N_post_C_1_7</t>
-  </si>
-  <si>
-    <t>N05_0</t>
-  </si>
-  <si>
-    <t>N_post_C_1_8</t>
-  </si>
-  <si>
-    <t>N05_1</t>
-  </si>
-  <si>
-    <t>N_post_C_1_9</t>
-  </si>
-  <si>
-    <t>N06_C</t>
-  </si>
-  <si>
-    <t>N06_C_0</t>
-  </si>
-  <si>
-    <t>N_post_C_2_0</t>
-  </si>
-  <si>
-    <t>N06_C_1</t>
-  </si>
-  <si>
-    <t>N_post_C_2_1</t>
-  </si>
-  <si>
-    <t>N07_0</t>
-  </si>
-  <si>
-    <t>N_post_C_2_2</t>
-  </si>
-  <si>
-    <t>N07_1</t>
-  </si>
-  <si>
-    <t>N08_C</t>
-  </si>
-  <si>
-    <t>N08_C_0</t>
-  </si>
-  <si>
-    <t>N_post_C_3_0</t>
-  </si>
-  <si>
-    <t>N08_C_1</t>
-  </si>
-  <si>
-    <t>N_post_C_3_1</t>
-  </si>
-  <si>
-    <t>N09_0</t>
-  </si>
-  <si>
-    <t>N_post_C_3_2</t>
-  </si>
-  <si>
-    <t>N09_1</t>
-  </si>
-  <si>
-    <t>N_pre_C_0_0</t>
-  </si>
-  <si>
-    <t>N_pre_C_0_1</t>
-  </si>
-  <si>
-    <t>N_pre_C_0_2</t>
-  </si>
-  <si>
-    <t>N_pre_C_0_3</t>
-  </si>
-  <si>
-    <t>N_pre_C_0_4</t>
-  </si>
-  <si>
-    <t>N03</t>
-  </si>
-  <si>
-    <t>N_pre_C_1_0</t>
-  </si>
-  <si>
-    <t>N_pre_C_1_1</t>
-  </si>
-  <si>
-    <t>N_pre_C_1_2</t>
-  </si>
-  <si>
-    <t>N_pre_C_1_3</t>
-  </si>
-  <si>
-    <t>N_pre_C_1_4</t>
-  </si>
-  <si>
-    <t>N_pre_C_1_5</t>
-  </si>
-  <si>
-    <t>N_pre_C_1_6</t>
-  </si>
-  <si>
-    <t>N_pre_C_1_7</t>
-  </si>
-  <si>
-    <t>N_pre_C_1_8</t>
-  </si>
-  <si>
-    <t>N_pre_C_1_9</t>
-  </si>
-  <si>
-    <t>N06</t>
-  </si>
-  <si>
-    <t>N_pre_C_2_0</t>
-  </si>
-  <si>
-    <t>N07</t>
-  </si>
-  <si>
-    <t>N_pre_C_2_2</t>
-  </si>
-  <si>
-    <t>N08</t>
-  </si>
-  <si>
-    <t>N_pre_C_3_0</t>
-  </si>
-  <si>
-    <t>N09</t>
-  </si>
-  <si>
-    <t>N_pre_C_3_2</t>
-  </si>
-  <si>
     <t>N10</t>
   </si>
   <si>
-    <t>Existing</t>
-  </si>
-  <si>
     <t>Segment</t>
   </si>
   <si>
@@ -862,22 +863,316 @@
   </si>
   <si>
     <t>N13</t>
+  </si>
+  <si>
+    <t>capacity</t>
+  </si>
+  <si>
+    <t>527617.1846909181</t>
+  </si>
+  <si>
+    <t>long term utilization</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>demand rampup</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>analysis start year</t>
+  </si>
+  <si>
+    <t>2020</t>
+  </si>
+  <si>
+    <t>operating life</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>installation months</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>TOPC</t>
+  </si>
+  <si>
+    <t>unit price</t>
+  </si>
+  <si>
+    <t>0.0</t>
+  </si>
+  <si>
+    <t>decay</t>
+  </si>
+  <si>
+    <t>support utilization</t>
+  </si>
+  <si>
+    <t>sunset years</t>
+  </si>
+  <si>
+    <t>commodity</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>Natural Gas-H2 Blend</t>
+  </si>
+  <si>
+    <t>unit</t>
+  </si>
+  <si>
+    <t>MMBTU</t>
+  </si>
+  <si>
+    <t>initial price</t>
+  </si>
+  <si>
+    <t>0.25</t>
+  </si>
+  <si>
+    <t>escalation</t>
+  </si>
+  <si>
+    <t>0.025</t>
+  </si>
+  <si>
+    <t>annual operating incentive</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>taxable</t>
+  </si>
+  <si>
+    <t>True</t>
+  </si>
+  <si>
+    <t>incidental revenue</t>
+  </si>
+  <si>
+    <t>credit card fees</t>
+  </si>
+  <si>
+    <t>sales tax</t>
+  </si>
+  <si>
+    <t>road tax</t>
+  </si>
+  <si>
+    <t>labor</t>
+  </si>
+  <si>
+    <t>rate</t>
+  </si>
+  <si>
+    <t>maintenance</t>
+  </si>
+  <si>
+    <t>rent</t>
+  </si>
+  <si>
+    <t>license and permit</t>
+  </si>
+  <si>
+    <t>non depr assets</t>
+  </si>
+  <si>
+    <t>end of proj sale non depr assets</t>
+  </si>
+  <si>
+    <t>installation cost</t>
+  </si>
+  <si>
+    <t>depr type</t>
+  </si>
+  <si>
+    <t>Straight line</t>
+  </si>
+  <si>
+    <t>depr period</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>depreciable</t>
+  </si>
+  <si>
+    <t>one time cap inct</t>
+  </si>
+  <si>
+    <t>MACRS</t>
+  </si>
+  <si>
+    <t>property tax and insurance</t>
+  </si>
+  <si>
+    <t>0.009</t>
+  </si>
+  <si>
+    <t>admin expense</t>
+  </si>
+  <si>
+    <t>0.005</t>
+  </si>
+  <si>
+    <t>tax loss carry forward years</t>
+  </si>
+  <si>
+    <t>capital gains tax rate</t>
+  </si>
+  <si>
+    <t>0.15</t>
+  </si>
+  <si>
+    <t>tax losses monetized</t>
+  </si>
+  <si>
+    <t>sell undepreciated cap</t>
+  </si>
+  <si>
+    <t>loan period if used</t>
+  </si>
+  <si>
+    <t>debt equity ratio of initial financing</t>
+  </si>
+  <si>
+    <t>0.62</t>
+  </si>
+  <si>
+    <t>debt interest rate</t>
+  </si>
+  <si>
+    <t>0.07</t>
+  </si>
+  <si>
+    <t>debt type</t>
+  </si>
+  <si>
+    <t>Revolving debt</t>
+  </si>
+  <si>
+    <t>total income tax rate</t>
+  </si>
+  <si>
+    <t>0.2574</t>
+  </si>
+  <si>
+    <t>cash onhand</t>
+  </si>
+  <si>
+    <t>general inflation rate</t>
+  </si>
+  <si>
+    <t>leverage after tax nominal discount rate</t>
+  </si>
+  <si>
+    <t>0.13</t>
+  </si>
+  <si>
+    <t>fraction of year operated</t>
+  </si>
+  <si>
+    <t>[0. 0. 0. 0. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1.
+ 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1.
+ 1. 1. 1. 1. 1. 1.]</t>
+  </si>
+  <si>
+    <t>New pipe CapEx</t>
+  </si>
+  <si>
+    <t>cost</t>
+  </si>
+  <si>
+    <t>depr_type</t>
+  </si>
+  <si>
+    <t>depr_period</t>
+  </si>
+  <si>
+    <t>refurb</t>
+  </si>
+  <si>
+    <t>[0]</t>
+  </si>
+  <si>
+    <t>New compression capacity CapEx</t>
+  </si>
+  <si>
+    <t>206997933.87205377</t>
+  </si>
+  <si>
+    <t>Refurbished compressor capacity CapEx</t>
+  </si>
+  <si>
+    <t>50748077.07023712</t>
+  </si>
+  <si>
+    <t>Supply compressor CapEx</t>
+  </si>
+  <si>
+    <t>Meter &amp; regulator station modification CapEx</t>
+  </si>
+  <si>
+    <t>10486757.29473448</t>
+  </si>
+  <si>
+    <t>Valve replacement CapEx</t>
+  </si>
+  <si>
+    <t>24862120.0</t>
+  </si>
+  <si>
+    <t>Original network residual value</t>
+  </si>
+  <si>
+    <t>Gas pressure regulation and metering station</t>
+  </si>
+  <si>
+    <t>Compressor fuel</t>
+  </si>
+  <si>
+    <t>{'2048': np.float64(27.046985282253413), '2049': np.float64(27.723159914309747), '2050': np.float64(28.416238912167486), '2051': np.float64(29.126644884971675), '2052': np.float64(29.85481100709596), '2053': np.float64(30.60118128227336), '2054': np.float64(31.366210814330188), '2055': np.float64(32.150366084688436), '2056': np.float64(32.954125236805645), '2057': np.float64(33.77797836772578), '2058': np.float64(34.62242782691893), '2059': np.float64(35.48798852259189), '2060': np.float64(36.37518823565669), '2061': np.float64(37.284567941548104), '2062': np.float64(38.2166821400868), '2063': np.float64(39.17209919358897), '2064': np.float64(40.151401673428694), '2065': np.float64(41.155186715264406), '2066': np.float64(42.18406638314601), '2067': np.float64(43.238668042724655), '2068': np.float64(44.319634743792776), '2069': np.float64(45.42762561238759), '2070': np.float64(46.56331625269728), '2071': np.float64(47.7273991590147), '2072': np.float64(48.92058413799006), '2073': np.float64(50.14359874143982), '2074': np.float64(51.3971887099758), '2075': np.float64(52.68211842772519), '2076': np.float64(53.99917138841832), '2077': np.float64(55.34915067312877), '2078': np.float64(56.732879439956996), '2079': np.float64(58.1512014259559), '2080': np.float64(59.604981461604794), '2081': np.float64(61.095105998144916), '2082': np.float64(62.62248364809852), '2020': np.float64(13.54723404173073), '2021': np.float64(13.885914892773997), '2022': np.float64(14.233062765093345), '2023': np.float64(14.588889334220678), '2024': np.float64(14.953611567576193), '2025': np.float64(15.327451856765595), '2026': np.float64(15.710638153184735), '2027': np.float64(16.103404107014356), '2028': np.float64(16.50598920968971), '2029': np.float64(16.918638939931952), '2030': np.float64(17.341604913430245), '2031': np.float64(17.775145036266004), '2032': np.float64(18.219523662172655), '2033': np.float64(18.675011753726963), '2034': np.float64(19.14188704757014), '2035': np.float64(19.62043422375939), '2036': np.float64(20.110945079353375), '2037': np.float64(20.613718706337206), '2038': np.float64(21.129061673995636), '2039': np.float64(21.65728821584552), '2040': np.float64(22.19872042124166), '2041': np.float64(22.7536884317727), '2042': np.float64(23.322530642567017), '2043': np.float64(23.90559390863119), '2044': np.float64(24.503233756346965), '2045': np.float64(25.11581460025564), '2046': np.float64(25.743709965262028), '2047': np.float64(26.387302714393577)}</t>
+  </si>
+  <si>
+    <t>usage</t>
+  </si>
+  <si>
+    <t>0.03539824745318141</t>
+  </si>
+  <si>
+    <t>Compressor fuel (electric)</t>
+  </si>
+  <si>
+    <t>Supply commpressor fuel (electric)</t>
+  </si>
+  <si>
+    <t>Supply commpressor fuel</t>
+  </si>
+  <si>
+    <t>In-line inspection</t>
+  </si>
+  <si>
+    <t>3277333.333333334</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -893,7 +1188,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -901,32 +1196,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1240,14 +1517,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="2" t="s">
+      <c r="A1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1256,28 +1533,28 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -1285,7 +1562,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -1293,7 +1570,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -1301,15 +1578,15 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B9">
         <v>0.5</v>
@@ -1317,7 +1594,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B10">
         <v>7.39</v>
@@ -1325,7 +1602,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B11">
         <v>4.40756</v>
@@ -1333,7 +1610,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B12">
         <v>0.07000000000000001</v>
@@ -1341,7 +1618,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B13">
         <v>3.325</v>
@@ -1349,63 +1626,63 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" t="b">
-        <v>1</v>
+        <v>25</v>
+      </c>
+      <c r="B17" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="B18">
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="B19">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20">
+        <v>29</v>
+      </c>
+      <c r="B20" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="B21" t="b">
         <v>0</v>
@@ -1413,39 +1690,100 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22" t="b">
-        <v>0</v>
+        <v>31</v>
+      </c>
+      <c r="B22">
+        <v>0.78</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="B23">
-        <v>0.78</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="B24">
-        <v>0.88</v>
+        <v>0.357</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>26</v>
-      </c>
-      <c r="B25">
-        <v>0.357</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>27</v>
+        <v>35</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>36</v>
+      </c>
+      <c r="B27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>42</v>
+      </c>
+      <c r="B32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" t="s">
+        <v>46</v>
+      </c>
+      <c r="B34">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1455,268 +1793,268 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H75"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B1" s="2" t="s">
+      <c r="A1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>37</v>
+      <c r="C1" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="B2">
-        <v>0.7952170069803824</v>
+        <v>0.7479461295393783</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="B4">
-        <v>0.1583445750742628</v>
+        <v>0.1325574732605284</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="B5">
-        <v>0.03229898434428223</v>
+        <v>0.0324980870264106</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="B6">
         <v>0</v>
       </c>
       <c r="C6" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="B7">
-        <v>0.006674373281496513</v>
+        <v>0.006715516544941178</v>
       </c>
       <c r="C7" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="B8">
-        <v>0.01582367788111964</v>
+        <v>0.01592122078444082</v>
       </c>
       <c r="C8" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="B9">
         <v>0</v>
       </c>
       <c r="C9" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="B10">
         <v>0.01701801172198347</v>
       </c>
       <c r="C10" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="B11">
-        <v>0.4935054437796491</v>
+        <v>0.4795483429153476</v>
       </c>
       <c r="C11" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B12">
         <v>0</v>
       </c>
       <c r="C12" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="B13">
         <v>0</v>
       </c>
       <c r="C13" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
+        <v>62</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14" t="s">
         <v>50</v>
-      </c>
-      <c r="B14">
-        <v>0</v>
-      </c>
-      <c r="C14" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="B15">
-        <v>0.008964272234900716</v>
+        <v>0</v>
       </c>
       <c r="C15" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="B16">
-        <v>0.05896294989798587</v>
+        <v>0</v>
       </c>
       <c r="C16" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B17">
-        <v>0.003624718764702249</v>
+        <v>0.008105411860109282</v>
       </c>
       <c r="C17" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="B18">
-        <v>4.40756</v>
+        <v>0.05210782572567367</v>
       </c>
       <c r="C18" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="B19">
-        <v>7.39</v>
+        <v>0.003474239699943219</v>
       </c>
       <c r="C19" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="B20">
-        <v>13.54723404173073</v>
+        <v>4.40756</v>
       </c>
       <c r="C20" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="B21">
-        <v>527617.1846909181</v>
+        <v>7.39</v>
       </c>
       <c r="C21" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="B22">
-        <v>21984.04936212159</v>
+        <v>13.54723404173073</v>
       </c>
       <c r="C22" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>527617.1846909181</v>
       </c>
       <c r="C23" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>21984.04936212159</v>
       </c>
       <c r="C24" t="s">
         <v>75</v>
@@ -1724,472 +2062,307 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="B25">
-        <v>21</v>
+        <v>0</v>
+      </c>
+      <c r="C25" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="B26">
-        <v>98102.37998896508</v>
+        <v>0</v>
       </c>
       <c r="C26" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="B27">
-        <v>19220.3037221165</v>
-      </c>
-      <c r="C27" t="s">
-        <v>72</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="B28">
-        <v>800.8459884215208</v>
+        <v>91604.78565493585</v>
       </c>
       <c r="C28" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>18676.72366424003</v>
       </c>
       <c r="C29" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>778.1968193433348</v>
       </c>
       <c r="C30" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="B31">
-        <v>248790569.1977327</v>
+        <v>0</v>
       </c>
       <c r="C31" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="B32">
+        <v>0</v>
+      </c>
+      <c r="C32" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" t="s">
+        <v>87</v>
+      </c>
+      <c r="B33">
+        <v>206997933.8720538</v>
+      </c>
+      <c r="C33" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" t="s">
+        <v>88</v>
+      </c>
+      <c r="B34">
         <v>50748077.07023712</v>
       </c>
-      <c r="C32" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" t="s">
-        <v>67</v>
-      </c>
-      <c r="B33">
+      <c r="C34" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" t="s">
+        <v>89</v>
+      </c>
+      <c r="B35">
         <v>10486757.29473448</v>
       </c>
-      <c r="C33" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" t="s">
-        <v>68</v>
-      </c>
-      <c r="B34">
+      <c r="C35" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" t="s">
+        <v>90</v>
+      </c>
+      <c r="B36">
         <v>24862120</v>
       </c>
-      <c r="C34" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" t="s">
-        <v>69</v>
-      </c>
-      <c r="B35">
+      <c r="C36" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" t="s">
+        <v>91</v>
+      </c>
+      <c r="B37">
+        <v>0</v>
+      </c>
+      <c r="C37" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" t="s">
+        <v>92</v>
+      </c>
+      <c r="B38">
+        <v>0</v>
+      </c>
+      <c r="C38" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" t="s">
+        <v>93</v>
+      </c>
+      <c r="B39">
         <v>24.24086700823207</v>
       </c>
-      <c r="C35" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8">
-      <c r="A39" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8">
-      <c r="A40" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8">
-      <c r="A41">
+      <c r="C39" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" t="s">
+        <v>95</v>
+      </c>
+      <c r="B40">
+        <v>49.91488829708958</v>
+      </c>
+      <c r="C40" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" t="s">
+        <v>97</v>
+      </c>
+      <c r="B41">
+        <v>9.612622785677301</v>
+      </c>
+      <c r="C41" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" t="s">
+        <v>100</v>
+      </c>
+      <c r="B47" t="s">
+        <v>101</v>
+      </c>
+      <c r="C47" t="s">
+        <v>102</v>
+      </c>
+      <c r="D47" t="s">
+        <v>103</v>
+      </c>
+      <c r="E47" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48">
         <v>650</v>
       </c>
-      <c r="B41">
+      <c r="B48">
         <v>400.0000000000002</v>
       </c>
-      <c r="C41" t="s">
-        <v>85</v>
-      </c>
-      <c r="D41" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8">
-      <c r="A45" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8">
-      <c r="A46" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G46" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H46" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8">
-      <c r="A50" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8">
-      <c r="A51" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="G51" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H51" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8">
-      <c r="A52" t="s">
-        <v>102</v>
-      </c>
-      <c r="B52">
-        <v>3.984783723618233</v>
-      </c>
-      <c r="C52">
-        <v>0</v>
-      </c>
-      <c r="D52">
-        <v>5343.674669046522</v>
-      </c>
-      <c r="E52">
-        <v>12506675.77274331</v>
-      </c>
-      <c r="F52">
-        <v>0</v>
-      </c>
-      <c r="G52">
-        <v>38.08569466312465</v>
-      </c>
-      <c r="H52">
-        <v>0</v>
+      <c r="C48" t="s">
+        <v>105</v>
+      </c>
+      <c r="D48" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" t="s">
-        <v>103</v>
-      </c>
-      <c r="B53">
-        <v>3.963972405680329</v>
-      </c>
-      <c r="C53">
-        <v>0</v>
-      </c>
-      <c r="D53">
-        <v>5315.766275465435</v>
-      </c>
-      <c r="E53">
-        <v>12475993.31860835</v>
-      </c>
-      <c r="F53">
-        <v>0</v>
-      </c>
-      <c r="G53">
-        <v>37.88678462044848</v>
-      </c>
-      <c r="H53">
-        <v>0</v>
+        <v>107</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" t="s">
-        <v>104</v>
-      </c>
-      <c r="B54">
-        <v>3.943302449008111</v>
-      </c>
-      <c r="C54">
-        <v>0</v>
-      </c>
-      <c r="D54">
-        <v>5288.047450168857</v>
-      </c>
-      <c r="E54">
-        <v>12445525.99409463</v>
-      </c>
-      <c r="F54">
-        <v>0</v>
-      </c>
-      <c r="G54">
-        <v>37.68922567795127</v>
-      </c>
-      <c r="H54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8">
-      <c r="A55" t="s">
-        <v>105</v>
-      </c>
-      <c r="B55">
-        <v>3.92279344934181</v>
-      </c>
-      <c r="C55">
-        <v>0</v>
-      </c>
-      <c r="D55">
-        <v>5260.544471436354</v>
-      </c>
-      <c r="E55">
-        <v>12415302.53629384</v>
-      </c>
-      <c r="F55">
-        <v>0</v>
-      </c>
-      <c r="G55">
-        <v>37.49320512744882</v>
-      </c>
-      <c r="H55">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8">
-      <c r="A56" t="s">
-        <v>106</v>
-      </c>
-      <c r="B56">
-        <v>3.902438955786296</v>
-      </c>
-      <c r="C56">
-        <v>0</v>
-      </c>
-      <c r="D56">
-        <v>5233.248688488538</v>
-      </c>
-      <c r="E56">
-        <v>12385313.28662439</v>
-      </c>
-      <c r="F56">
-        <v>0</v>
-      </c>
-      <c r="G56">
-        <v>37.29866131269092</v>
-      </c>
-      <c r="H56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8">
-      <c r="A57" t="s">
-        <v>107</v>
-      </c>
-      <c r="B57">
-        <v>3.88221965980898</v>
-      </c>
-      <c r="C57">
-        <v>12.5</v>
-      </c>
-      <c r="D57">
-        <v>0</v>
-      </c>
-      <c r="E57">
-        <v>0</v>
-      </c>
-      <c r="F57">
-        <v>16916025.69007904</v>
-      </c>
-      <c r="G57">
-        <v>37.10540968692987</v>
-      </c>
-      <c r="H57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8">
-      <c r="A58" t="s">
+        <v>100</v>
+      </c>
+      <c r="B54" t="s">
+        <v>101</v>
+      </c>
+      <c r="C54" t="s">
         <v>108</v>
       </c>
-      <c r="B58">
-        <v>3.916977767373811</v>
-      </c>
-      <c r="C58">
-        <v>0</v>
-      </c>
-      <c r="D58">
-        <v>5252.745525603627</v>
-      </c>
-      <c r="E58">
-        <v>12406733.35113453</v>
-      </c>
-      <c r="F58">
-        <v>0</v>
-      </c>
-      <c r="G58">
-        <v>37.4376201062648</v>
-      </c>
-      <c r="H58">
-        <v>0</v>
+      <c r="D54" t="s">
+        <v>103</v>
+      </c>
+      <c r="E54" t="s">
+        <v>109</v>
+      </c>
+      <c r="F54" t="s">
+        <v>110</v>
+      </c>
+      <c r="G54" t="s">
+        <v>111</v>
+      </c>
+      <c r="H54" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" t="s">
-        <v>109</v>
-      </c>
-      <c r="B59">
-        <v>3.896675845842932</v>
-      </c>
-      <c r="C59">
-        <v>0</v>
-      </c>
-      <c r="D59">
-        <v>5225.520242792289</v>
-      </c>
-      <c r="E59">
-        <v>12376823.40030325</v>
-      </c>
-      <c r="F59">
-        <v>0</v>
-      </c>
-      <c r="G59">
-        <v>37.24357876346446</v>
-      </c>
-      <c r="H59">
-        <v>0</v>
+        <v>113</v>
       </c>
     </row>
     <row r="60" spans="1:8">
       <c r="A60" t="s">
-        <v>110</v>
-      </c>
-      <c r="B60">
-        <v>2.835985783307106</v>
-      </c>
-      <c r="C60">
-        <v>0</v>
-      </c>
-      <c r="D60">
-        <v>3803.113655130495</v>
-      </c>
-      <c r="E60">
-        <v>10823138.61767111</v>
-      </c>
-      <c r="F60">
-        <v>0</v>
-      </c>
-      <c r="G60">
-        <v>27.10573423892676</v>
-      </c>
-      <c r="H60">
-        <v>0</v>
+        <v>114</v>
+      </c>
+      <c r="B60" t="s">
+        <v>115</v>
+      </c>
+      <c r="C60" t="s">
+        <v>116</v>
+      </c>
+      <c r="D60" t="s">
+        <v>117</v>
+      </c>
+      <c r="E60" t="s">
+        <v>118</v>
+      </c>
+      <c r="F60" t="s">
+        <v>119</v>
+      </c>
+      <c r="G60" t="s">
+        <v>120</v>
+      </c>
+      <c r="H60" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="61" spans="1:8">
       <c r="A61" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="B61">
-        <v>2.116270395524172</v>
+        <v>6.075880798904029</v>
       </c>
       <c r="C61">
         <v>0</v>
       </c>
       <c r="D61">
-        <v>2837.960925805825</v>
+        <v>8147.877668946281</v>
       </c>
       <c r="E61">
-        <v>9953691.026075777</v>
+        <v>15624217.33691421</v>
       </c>
       <c r="F61">
         <v>0</v>
       </c>
       <c r="G61">
-        <v>20.22685136732043</v>
+        <v>58.07194492013306</v>
       </c>
       <c r="H61">
         <v>0</v>
@@ -2197,25 +2370,25 @@
     </row>
     <row r="62" spans="1:8">
       <c r="A62" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="B62">
-        <v>2.109061500416896</v>
+        <v>6.023480766828984</v>
       </c>
       <c r="C62">
         <v>0</v>
       </c>
       <c r="D62">
-        <v>2828.293653289066</v>
+        <v>8077.608177933004</v>
       </c>
       <c r="E62">
-        <v>9953691.026075777</v>
+        <v>15545258.93675933</v>
       </c>
       <c r="F62">
         <v>0</v>
       </c>
       <c r="G62">
-        <v>20.15795031849139</v>
+        <v>57.57111682998618</v>
       </c>
       <c r="H62">
         <v>0</v>
@@ -2223,25 +2396,25 @@
     </row>
     <row r="63" spans="1:8">
       <c r="A63" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="B63">
-        <v>2.1019127014274</v>
+        <v>5.971891349520104</v>
       </c>
       <c r="C63">
         <v>0</v>
       </c>
       <c r="D63">
-        <v>2818.706970868172</v>
+        <v>8008.425737533449</v>
       </c>
       <c r="E63">
-        <v>9953691.026075777</v>
+        <v>15467564.03912066</v>
       </c>
       <c r="F63">
         <v>0</v>
       </c>
       <c r="G63">
-        <v>20.0896236552629</v>
+        <v>57.07803641916518</v>
       </c>
       <c r="H63">
         <v>0</v>
@@ -2249,25 +2422,25 @@
     </row>
     <row r="64" spans="1:8">
       <c r="A64" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="B64">
-        <v>2.094768760207821</v>
+        <v>5.921102770440302</v>
       </c>
       <c r="C64">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="D64">
-        <v>2809.126802813892</v>
+        <v>0</v>
       </c>
       <c r="E64">
-        <v>9953691.026075777</v>
+        <v>0</v>
       </c>
       <c r="F64">
-        <v>0</v>
+        <v>16916025.69007904</v>
       </c>
       <c r="G64">
-        <v>20.02134342154093</v>
+        <v>56.5926102456586</v>
       </c>
       <c r="H64">
         <v>0</v>
@@ -2275,25 +2448,25 @@
     </row>
     <row r="65" spans="1:8">
       <c r="A65" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="B65">
-        <v>2.087665669835559</v>
+        <v>5.370342173923548</v>
       </c>
       <c r="C65">
         <v>0</v>
       </c>
       <c r="D65">
-        <v>2799.601416562882</v>
+        <v>7201.736262074955</v>
       </c>
       <c r="E65">
-        <v>9953691.026075777</v>
+        <v>14564695.19587668</v>
       </c>
       <c r="F65">
         <v>0</v>
       </c>
       <c r="G65">
-        <v>19.95345363131741</v>
+        <v>51.32856045869275</v>
       </c>
       <c r="H65">
         <v>0</v>
@@ -2301,25 +2474,25 @@
     </row>
     <row r="66" spans="1:8">
       <c r="A66" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="B66">
-        <v>2.080632413896195</v>
+        <v>4.298188663193453</v>
       </c>
       <c r="C66">
         <v>0</v>
       </c>
       <c r="D66">
-        <v>2790.169679683076</v>
+        <v>5763.956961115684</v>
       </c>
       <c r="E66">
-        <v>9953691.026075777</v>
+        <v>12969554.36951518</v>
       </c>
       <c r="F66">
         <v>0</v>
       </c>
       <c r="G66">
-        <v>19.88623130338864</v>
+        <v>41.08115079386256</v>
       </c>
       <c r="H66">
         <v>0</v>
@@ -2327,25 +2500,25 @@
     </row>
     <row r="67" spans="1:8">
       <c r="A67" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="B67">
-        <v>2.073629831215724</v>
+        <v>2.831196589435429</v>
       </c>
       <c r="C67">
         <v>0</v>
       </c>
       <c r="D67">
-        <v>2780.77907625691</v>
+        <v>3796.691250364699</v>
       </c>
       <c r="E67">
-        <v>9953691.026075777</v>
+        <v>10816163.45383709</v>
       </c>
       <c r="F67">
         <v>0</v>
       </c>
       <c r="G67">
-        <v>19.81930214378559</v>
+        <v>27.05996016732582</v>
       </c>
       <c r="H67">
         <v>0</v>
@@ -2353,25 +2526,25 @@
     </row>
     <row r="68" spans="1:8">
       <c r="A68" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="B68">
-        <v>2.066635615830844</v>
+        <v>2.818013891988561</v>
       </c>
       <c r="C68">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="D68">
-        <v>0</v>
+        <v>3779.0129894345</v>
       </c>
       <c r="E68">
-        <v>0</v>
+        <v>10796965.52906065</v>
       </c>
       <c r="F68">
-        <v>16916025.69007904</v>
+        <v>0</v>
       </c>
       <c r="G68">
-        <v>19.7524529569708</v>
+        <v>26.93396281725086</v>
       </c>
       <c r="H68">
         <v>0</v>
@@ -2379,25 +2552,25 @@
     </row>
     <row r="69" spans="1:8">
       <c r="A69" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="B69">
-        <v>4.80660821951508</v>
+        <v>2.804937926775326</v>
       </c>
       <c r="C69">
         <v>0</v>
       </c>
       <c r="D69">
-        <v>6445.757754534112</v>
+        <v>3761.477858564248</v>
       </c>
       <c r="E69">
-        <v>13723730.8144163</v>
+        <v>10777925.72858675</v>
       </c>
       <c r="F69">
         <v>0</v>
       </c>
       <c r="G69">
-        <v>45.94051414351117</v>
+        <v>26.80898559061113</v>
       </c>
       <c r="H69">
         <v>0</v>
@@ -2405,25 +2578,25 @@
     </row>
     <row r="70" spans="1:8">
       <c r="A70" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="B70">
-        <v>4.765817931723653</v>
+        <v>2.791967405497823</v>
       </c>
       <c r="C70">
         <v>0</v>
       </c>
       <c r="D70">
-        <v>6391.057162800053</v>
+        <v>3744.08413012069</v>
       </c>
       <c r="E70">
-        <v>13663074.09012518</v>
+        <v>10759042.11131523</v>
       </c>
       <c r="F70">
         <v>0</v>
       </c>
       <c r="G70">
-        <v>45.55064945980518</v>
+        <v>26.68501617413599</v>
       </c>
       <c r="H70">
         <v>0</v>
@@ -2431,25 +2604,25 @@
     </row>
     <row r="71" spans="1:8">
       <c r="A71" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="B71">
-        <v>4.725670648042011</v>
+        <v>2.779101144517401</v>
       </c>
       <c r="C71">
         <v>0</v>
       </c>
       <c r="D71">
-        <v>6337.218852437298</v>
+        <v>3726.830216820725</v>
       </c>
       <c r="E71">
-        <v>13603398.99923224</v>
+        <v>10740312.89006076</v>
       </c>
       <c r="F71">
         <v>0</v>
       </c>
       <c r="G71">
-        <v>45.16693046928879</v>
+        <v>26.56204325486512</v>
       </c>
       <c r="H71">
         <v>0</v>
@@ -2457,10 +2630,10 @@
     </row>
     <row r="72" spans="1:8">
       <c r="A72" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="B72">
-        <v>4.686038287642569</v>
+        <v>2.76633793671081</v>
       </c>
       <c r="C72">
         <v>12.5</v>
@@ -2475,7 +2648,7 @@
         <v>16916025.69007904</v>
       </c>
       <c r="G72">
-        <v>44.78813300331705</v>
+        <v>26.44005529537746</v>
       </c>
       <c r="H72">
         <v>0</v>
@@ -2483,25 +2656,25 @@
     </row>
     <row r="73" spans="1:8">
       <c r="A73" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="B73">
-        <v>4.647018783510063</v>
+        <v>4.528467102579145</v>
       </c>
       <c r="C73">
         <v>0</v>
       </c>
       <c r="D73">
-        <v>6231.745129062665</v>
+        <v>6072.764953900685</v>
       </c>
       <c r="E73">
-        <v>13486563.75308981</v>
+        <v>13310641.584289</v>
       </c>
       <c r="F73">
         <v>0</v>
       </c>
       <c r="G73">
-        <v>44.41519308402132</v>
+        <v>43.28210194660938</v>
       </c>
       <c r="H73">
         <v>0</v>
@@ -2509,25 +2682,25 @@
     </row>
     <row r="74" spans="1:8">
       <c r="A74" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="B74">
-        <v>4.608497794183321</v>
+        <v>4.492811504549465</v>
       </c>
       <c r="C74">
         <v>0</v>
       </c>
       <c r="D74">
-        <v>6180.087711955716</v>
+        <v>6024.950083830923</v>
       </c>
       <c r="E74">
-        <v>13429377.21872473</v>
+        <v>13257774.32459174</v>
       </c>
       <c r="F74">
         <v>0</v>
       </c>
       <c r="G74">
-        <v>44.04701786062734</v>
+        <v>42.94131350894822</v>
       </c>
       <c r="H74">
         <v>0</v>
@@ -2535,27 +2708,131 @@
     </row>
     <row r="75" spans="1:8">
       <c r="A75" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="B75">
-        <v>4.570561121208711</v>
+        <v>4.457667619600001</v>
       </c>
       <c r="C75">
         <v>0</v>
       </c>
       <c r="D75">
-        <v>6129.213874763306</v>
+        <v>5977.821431235994</v>
       </c>
       <c r="E75">
-        <v>13373080.86214064</v>
+        <v>13205685.28860052</v>
       </c>
       <c r="F75">
         <v>0</v>
       </c>
       <c r="G75">
-        <v>43.6844274056217</v>
+        <v>42.60541591342052</v>
       </c>
       <c r="H75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76" t="s">
+        <v>137</v>
+      </c>
+      <c r="B76">
+        <v>4.423005960727749</v>
+      </c>
+      <c r="C76">
+        <v>12.5</v>
+      </c>
+      <c r="D76">
+        <v>0</v>
+      </c>
+      <c r="E76">
+        <v>0</v>
+      </c>
+      <c r="F76">
+        <v>16916025.69007904</v>
+      </c>
+      <c r="G76">
+        <v>42.27412732967593</v>
+      </c>
+      <c r="H76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="A77" t="s">
+        <v>138</v>
+      </c>
+      <c r="B77">
+        <v>4.388831871894594</v>
+      </c>
+      <c r="C77">
+        <v>0</v>
+      </c>
+      <c r="D77">
+        <v>5885.511316848089</v>
+      </c>
+      <c r="E77">
+        <v>13103715.43741976</v>
+      </c>
+      <c r="F77">
+        <v>0</v>
+      </c>
+      <c r="G77">
+        <v>41.94749883413785</v>
+      </c>
+      <c r="H77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
+      <c r="A78" t="s">
+        <v>139</v>
+      </c>
+      <c r="B78">
+        <v>4.355123891449361</v>
+      </c>
+      <c r="C78">
+        <v>0</v>
+      </c>
+      <c r="D78">
+        <v>5840.308240911422</v>
+      </c>
+      <c r="E78">
+        <v>13053809.19711511</v>
+      </c>
+      <c r="F78">
+        <v>0</v>
+      </c>
+      <c r="G78">
+        <v>41.62532530102022</v>
+      </c>
+      <c r="H78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
+      <c r="A79" t="s">
+        <v>140</v>
+      </c>
+      <c r="B79">
+        <v>4.321880639588149</v>
+      </c>
+      <c r="C79">
+        <v>0</v>
+      </c>
+      <c r="D79">
+        <v>5795.728375300499</v>
+      </c>
+      <c r="E79">
+        <v>13004608.44899116</v>
+      </c>
+      <c r="F79">
+        <v>0</v>
+      </c>
+      <c r="G79">
+        <v>41.30759354245797</v>
+      </c>
+      <c r="H79">
         <v>0</v>
       </c>
     </row>
@@ -2566,63 +2843,63 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R45"/>
+  <dimension ref="A1:R40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="R1" s="2" t="s">
+      <c r="A1" t="s">
         <v>141</v>
+      </c>
+      <c r="B1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D1" t="s">
+        <v>144</v>
+      </c>
+      <c r="E1" t="s">
+        <v>145</v>
+      </c>
+      <c r="F1" t="s">
+        <v>146</v>
+      </c>
+      <c r="G1" t="s">
+        <v>147</v>
+      </c>
+      <c r="H1" t="s">
+        <v>103</v>
+      </c>
+      <c r="I1" t="s">
+        <v>148</v>
+      </c>
+      <c r="J1" t="s">
+        <v>149</v>
+      </c>
+      <c r="K1" t="s">
+        <v>150</v>
+      </c>
+      <c r="L1" t="s">
+        <v>101</v>
+      </c>
+      <c r="M1" t="s">
+        <v>151</v>
+      </c>
+      <c r="N1" t="s">
+        <v>152</v>
+      </c>
+      <c r="O1" t="s">
+        <v>153</v>
+      </c>
+      <c r="P1" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>155</v>
+      </c>
+      <c r="R1" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -2630,55 +2907,55 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="C2" t="s">
-        <v>186</v>
+        <v>158</v>
       </c>
       <c r="D2" t="s">
-        <v>230</v>
+        <v>159</v>
       </c>
       <c r="E2" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F2">
-        <v>102.4882090100769</v>
+        <v>102.3869627634882</v>
       </c>
       <c r="G2">
         <v>650</v>
       </c>
       <c r="H2" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I2">
         <v>9.525</v>
       </c>
       <c r="J2" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K2">
         <v>4.71984827318464</v>
       </c>
       <c r="L2">
-        <v>11.66666666666667</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="M2">
-        <v>7.249328333333335</v>
+        <v>8.284946666666665</v>
       </c>
       <c r="N2">
         <v>4719848.27318464</v>
       </c>
       <c r="O2">
-        <v>4215363.528785638</v>
+        <v>4153318.623558146</v>
       </c>
       <c r="P2">
-        <v>17.92866114156495</v>
+        <v>19.67128147268389</v>
       </c>
       <c r="Q2">
-        <v>0.02950040522764811</v>
+        <v>0.03276800803752088</v>
       </c>
       <c r="R2">
-        <v>30.53340743745198</v>
+        <v>30.39204249800516</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -2686,55 +2963,55 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="C3" t="s">
-        <v>187</v>
+        <v>159</v>
       </c>
       <c r="D3" t="s">
-        <v>188</v>
+        <v>162</v>
       </c>
       <c r="E3" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F3">
-        <v>102.3175354415728</v>
+        <v>102.386964486603</v>
       </c>
       <c r="G3">
         <v>650</v>
       </c>
       <c r="H3" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I3">
         <v>9.525</v>
       </c>
       <c r="J3" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K3">
         <v>4.71984827318464</v>
       </c>
       <c r="L3">
-        <v>1.666666666666668</v>
+        <v>4.166666666666666</v>
       </c>
       <c r="M3">
-        <v>1.035618333333334</v>
+        <v>2.589045833333333</v>
       </c>
       <c r="N3">
-        <v>4719848.27318464</v>
+        <v>4153318.623558146</v>
       </c>
       <c r="O3">
-        <v>4651355.367264377</v>
+        <v>3960095.808721507</v>
       </c>
       <c r="P3">
-        <v>17.74582313216201</v>
+        <v>20.60798126663862</v>
       </c>
       <c r="Q3">
-        <v>0.02915255516971851</v>
+        <v>0.03437276927843772</v>
       </c>
       <c r="R3">
-        <v>29.06677128448647</v>
+        <v>31.10722591745218</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -2742,55 +3019,55 @@
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="C4" t="s">
-        <v>188</v>
+        <v>164</v>
       </c>
       <c r="D4" t="s">
-        <v>231</v>
+        <v>165</v>
       </c>
       <c r="E4" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F4">
-        <v>102.3175357530185</v>
+        <v>102.1258398129035</v>
       </c>
       <c r="G4">
         <v>650</v>
       </c>
       <c r="H4" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I4">
         <v>9.525</v>
       </c>
       <c r="J4" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K4">
         <v>4.71984827318464</v>
       </c>
       <c r="L4">
-        <v>9.999999999999998</v>
+        <v>9.166666666666668</v>
       </c>
       <c r="M4">
-        <v>6.213709999999999</v>
+        <v>5.695900833333334</v>
       </c>
       <c r="N4">
-        <v>4651355.367264377</v>
+        <v>4719848.27318464</v>
       </c>
       <c r="O4">
-        <v>4217106.914927895</v>
+        <v>4340123.800010766</v>
       </c>
       <c r="P4">
-        <v>17.78464262534786</v>
+        <v>18.79554403921967</v>
       </c>
       <c r="Q4">
-        <v>0.02926324303264966</v>
+        <v>0.03127150549975922</v>
       </c>
       <c r="R4">
-        <v>30.52709273110587</v>
+        <v>29.74579096043793</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -2798,55 +3075,55 @@
         <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="C5" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="D5" t="s">
-        <v>190</v>
+        <v>167</v>
       </c>
       <c r="E5" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F5">
-        <v>102.147197907504</v>
+        <v>102.1258399581034</v>
       </c>
       <c r="G5">
         <v>650</v>
       </c>
       <c r="H5" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I5">
         <v>9.525</v>
       </c>
       <c r="J5" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K5">
         <v>4.71984827318464</v>
       </c>
       <c r="L5">
-        <v>3.333333333333336</v>
+        <v>8.333333333333332</v>
       </c>
       <c r="M5">
-        <v>2.071236666666668</v>
+        <v>5.178091666666666</v>
       </c>
       <c r="N5">
-        <v>4719848.27318464</v>
+        <v>4340123.800010766</v>
       </c>
       <c r="O5">
-        <v>4582296.713969789</v>
+        <v>3964249.023480296</v>
       </c>
       <c r="P5">
-        <v>17.74210438397871</v>
+        <v>20.5344060696298</v>
       </c>
       <c r="Q5">
-        <v>0.02915396650060045</v>
+        <v>0.03424907870710304</v>
       </c>
       <c r="R5">
-        <v>29.2849046925862</v>
+        <v>31.09131879370828</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -2854,55 +3131,55 @@
         <v>0</v>
       </c>
       <c r="B6" t="s">
-        <v>146</v>
+        <v>168</v>
       </c>
       <c r="C6" t="s">
-        <v>190</v>
+        <v>169</v>
       </c>
       <c r="D6" t="s">
-        <v>232</v>
+        <v>170</v>
       </c>
       <c r="E6" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F6">
-        <v>102.1471979453405</v>
+        <v>101.8668857106812</v>
       </c>
       <c r="G6">
         <v>650</v>
       </c>
       <c r="H6" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I6">
         <v>9.525</v>
       </c>
       <c r="J6" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K6">
         <v>4.71984827318464</v>
       </c>
       <c r="L6">
-        <v>8.333333333333332</v>
+        <v>5</v>
       </c>
       <c r="M6">
-        <v>5.178091666666666</v>
+        <v>3.106855</v>
       </c>
       <c r="N6">
-        <v>4582296.713969789</v>
+        <v>4719848.27318464</v>
       </c>
       <c r="O6">
-        <v>4218842.598709397</v>
+        <v>4517629.51757387</v>
       </c>
       <c r="P6">
-        <v>17.77452394031071</v>
+        <v>18.02726050270281</v>
       </c>
       <c r="Q6">
-        <v>0.02924640506297461</v>
+        <v>0.02996006712745475</v>
       </c>
       <c r="R6">
-        <v>30.52080981378644</v>
+        <v>29.16850996485588</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -2910,55 +3187,55 @@
         <v>0</v>
       </c>
       <c r="B7" t="s">
-        <v>147</v>
+        <v>171</v>
       </c>
       <c r="C7" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
       <c r="D7" t="s">
-        <v>192</v>
+        <v>172</v>
       </c>
       <c r="E7" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F7">
-        <v>101.9776761610612</v>
+        <v>101.8668857209616</v>
       </c>
       <c r="G7">
         <v>650</v>
       </c>
       <c r="H7" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I7">
         <v>9.525</v>
       </c>
       <c r="J7" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K7">
         <v>4.71984827318464</v>
       </c>
       <c r="L7">
-        <v>5</v>
+        <v>12.5</v>
       </c>
       <c r="M7">
-        <v>3.106855</v>
+        <v>7.7671375</v>
       </c>
       <c r="N7">
-        <v>4719848.27318464</v>
+        <v>4517629.51757387</v>
       </c>
       <c r="O7">
-        <v>4512641.904149927</v>
+        <v>3968352.11991846</v>
       </c>
       <c r="P7">
-        <v>17.73854013572298</v>
+        <v>20.46166931724036</v>
       </c>
       <c r="Q7">
-        <v>0.02915555407357753</v>
+        <v>0.03412680609728763</v>
       </c>
       <c r="R7">
-        <v>29.51014135056064</v>
+        <v>31.07562756571341</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -2966,55 +3243,55 @@
         <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>148</v>
+        <v>173</v>
       </c>
       <c r="C8" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="D8" t="s">
-        <v>233</v>
+        <v>175</v>
       </c>
       <c r="E8" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F8">
-        <v>101.9776761648549</v>
+        <v>101.6101429338241</v>
       </c>
       <c r="G8">
         <v>650</v>
       </c>
       <c r="H8" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I8">
         <v>9.525</v>
       </c>
       <c r="J8" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K8">
         <v>4.71984827318464</v>
       </c>
       <c r="L8">
-        <v>6.666666666666664</v>
+        <v>2.5</v>
       </c>
       <c r="M8">
-        <v>4.142473333333332</v>
+        <v>1.5534275</v>
       </c>
       <c r="N8">
-        <v>4512641.904149927</v>
+        <v>4719848.27318464</v>
       </c>
       <c r="O8">
-        <v>4220568.35887037</v>
+        <v>4620320.376724417</v>
       </c>
       <c r="P8">
-        <v>17.76453231085767</v>
+        <v>17.59080821944845</v>
       </c>
       <c r="Q8">
-        <v>0.02922977745526039</v>
+        <v>0.02921640611731472</v>
       </c>
       <c r="R8">
-        <v>30.51456666306295</v>
+        <v>28.84963064393551</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -3022,167 +3299,167 @@
         <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>149</v>
+        <v>176</v>
       </c>
       <c r="C9" t="s">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c r="D9" t="s">
-        <v>194</v>
+        <v>177</v>
       </c>
       <c r="E9" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F9">
-        <v>101.8090283884677</v>
+        <v>101.6101429344213</v>
       </c>
       <c r="G9">
         <v>650</v>
       </c>
       <c r="H9" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I9">
         <v>9.525</v>
       </c>
       <c r="J9" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K9">
         <v>4.71984827318464</v>
       </c>
       <c r="L9">
-        <v>8.333333333333336</v>
+        <v>15</v>
       </c>
       <c r="M9">
-        <v>5.178091666666668</v>
+        <v>9.320565</v>
       </c>
       <c r="N9">
-        <v>4719848.27318464</v>
+        <v>4620320.376724417</v>
       </c>
       <c r="O9">
-        <v>4370233.447551202</v>
+        <v>3972405.119967355</v>
       </c>
       <c r="P9">
-        <v>17.7612176193511</v>
+        <v>20.38977393618725</v>
       </c>
       <c r="Q9">
-        <v>0.02920813616158855</v>
+        <v>0.03400595603715324</v>
       </c>
       <c r="R9">
-        <v>29.98728929348979</v>
+        <v>31.06015121900328</v>
       </c>
     </row>
     <row r="10" spans="1:18">
       <c r="A10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>150</v>
+        <v>178</v>
       </c>
       <c r="C10" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="D10" t="s">
-        <v>234</v>
+        <v>180</v>
       </c>
       <c r="E10" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F10">
-        <v>101.8090283887959</v>
+        <v>101.3555832352016</v>
       </c>
       <c r="G10">
         <v>650</v>
       </c>
       <c r="H10" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I10">
         <v>9.525</v>
       </c>
       <c r="J10" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K10">
         <v>4.71984827318464</v>
       </c>
       <c r="L10">
-        <v>3.333333333333329</v>
+        <v>15.75</v>
       </c>
       <c r="M10">
-        <v>2.071236666666664</v>
+        <v>9.786593249999999</v>
       </c>
       <c r="N10">
-        <v>4370233.447551202</v>
+        <v>4719848.27318464</v>
       </c>
       <c r="O10">
-        <v>4222284.9006737</v>
+        <v>4056742.542626799</v>
       </c>
       <c r="P10">
-        <v>17.77429259651771</v>
+        <v>19.92580642287422</v>
       </c>
       <c r="Q10">
-        <v>0.02924565068272606</v>
+        <v>0.03321322994865648</v>
       </c>
       <c r="R10">
-        <v>30.50836065988065</v>
+        <v>30.74326626494882</v>
       </c>
     </row>
     <row r="11" spans="1:18">
       <c r="A11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>151</v>
+        <v>181</v>
       </c>
       <c r="C11" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="D11" t="s">
-        <v>235</v>
+        <v>182</v>
       </c>
       <c r="E11" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F11">
-        <v>101.6412550050389</v>
+        <v>101.3555832352331</v>
       </c>
       <c r="G11">
         <v>650</v>
       </c>
       <c r="H11" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I11">
         <v>9.525</v>
       </c>
       <c r="J11" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K11">
         <v>4.71984827318464</v>
       </c>
       <c r="L11">
-        <v>11.66666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="M11">
-        <v>7.249328333333335</v>
+        <v>0.3106855</v>
       </c>
       <c r="N11">
-        <v>4719848.27318464</v>
+        <v>4056742.542626799</v>
       </c>
       <c r="O11">
-        <v>4223994.499606662</v>
+        <v>4033949.605008089</v>
       </c>
       <c r="P11">
-        <v>17.78433592228278</v>
+        <v>20.0357303239316</v>
       </c>
       <c r="Q11">
-        <v>0.02926199018108765</v>
+        <v>0.03340156280790203</v>
       </c>
       <c r="R11">
-        <v>30.50218352005824</v>
+        <v>30.82794970815699</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -3190,55 +3467,55 @@
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>152</v>
+        <v>183</v>
       </c>
       <c r="C12" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="D12" t="s">
-        <v>236</v>
+        <v>185</v>
       </c>
       <c r="E12" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F12">
-        <v>101.474350836439</v>
+        <v>101.1247017835448</v>
       </c>
       <c r="G12">
         <v>650</v>
       </c>
       <c r="H12" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I12">
         <v>9.525</v>
       </c>
       <c r="J12" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K12">
         <v>4.71984827318464</v>
       </c>
       <c r="L12">
-        <v>11.81818181818182</v>
+        <v>15.25</v>
       </c>
       <c r="M12">
-        <v>7.343475454545456</v>
+        <v>9.475907749999999</v>
       </c>
       <c r="N12">
         <v>4719848.27318464</v>
       </c>
       <c r="O12">
-        <v>4218886.028599959</v>
+        <v>4082487.92356313</v>
       </c>
       <c r="P12">
-        <v>17.75752079348137</v>
+        <v>19.7579752911947</v>
       </c>
       <c r="Q12">
-        <v>0.0292184231796562</v>
+        <v>0.03292782373801152</v>
       </c>
       <c r="R12">
-        <v>30.52065265378209</v>
+        <v>30.64844774243356</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -3246,55 +3523,55 @@
         <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>153</v>
+        <v>186</v>
       </c>
       <c r="C13" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="D13" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="E13" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F13">
-        <v>101.3059523458698</v>
+        <v>83.46637180767628</v>
       </c>
       <c r="G13">
         <v>650</v>
       </c>
       <c r="H13" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I13">
         <v>9.525</v>
       </c>
       <c r="J13" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K13">
         <v>4.71984827318464</v>
       </c>
       <c r="L13">
-        <v>3.93181818181818</v>
+        <v>1</v>
       </c>
       <c r="M13">
-        <v>2.443117795454544</v>
+        <v>0.621371</v>
       </c>
       <c r="N13">
-        <v>4719848.27318464</v>
+        <v>4082487.92356313</v>
       </c>
       <c r="O13">
-        <v>4559825.285667413</v>
+        <v>4051491.156438908</v>
       </c>
       <c r="P13">
-        <v>17.60520770192851</v>
+        <v>16.42967898649563</v>
       </c>
       <c r="Q13">
-        <v>0.02893139793841922</v>
+        <v>0.02738669048834791</v>
       </c>
       <c r="R13">
-        <v>29.35700417835938</v>
+        <v>30.7627150548208</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -3302,55 +3579,55 @@
         <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>154</v>
+        <v>188</v>
       </c>
       <c r="C14" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="D14" t="s">
-        <v>237</v>
+        <v>190</v>
       </c>
       <c r="E14" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F14">
-        <v>101.3059523458701</v>
+        <v>83.28158431927821</v>
       </c>
       <c r="G14">
         <v>650</v>
       </c>
       <c r="H14" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I14">
         <v>9.525</v>
       </c>
       <c r="J14" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K14">
         <v>4.71984827318464</v>
       </c>
       <c r="L14">
-        <v>7.88636363636364</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="M14">
-        <v>4.900357659090911</v>
+        <v>9.424126833333336</v>
       </c>
       <c r="N14">
-        <v>4559825.285667413</v>
+        <v>4719848.27318464</v>
       </c>
       <c r="O14">
-        <v>4220602.97408973</v>
+        <v>4296588.012048371</v>
       </c>
       <c r="P14">
-        <v>17.63567916261244</v>
+        <v>15.47915226989046</v>
       </c>
       <c r="Q14">
-        <v>0.02901775864034787</v>
+        <v>0.02576092540141354</v>
       </c>
       <c r="R14">
-        <v>30.51444147741832</v>
+        <v>29.89268932890086</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -3358,55 +3635,55 @@
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>155</v>
+        <v>191</v>
       </c>
       <c r="C15" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="D15" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="E15" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F15">
-        <v>101.1384266742019</v>
+        <v>83.28158431927739</v>
       </c>
       <c r="G15">
         <v>650</v>
       </c>
       <c r="H15" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I15">
         <v>9.525</v>
       </c>
       <c r="J15" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K15">
         <v>4.71984827318464</v>
       </c>
       <c r="L15">
-        <v>7.86363636363636</v>
+        <v>1.083333333333329</v>
       </c>
       <c r="M15">
-        <v>4.886235590909089</v>
+        <v>0.673151916666664</v>
       </c>
       <c r="N15">
-        <v>4719848.27318464</v>
+        <v>4296588.012048371</v>
       </c>
       <c r="O15">
-        <v>4395076.944624769</v>
+        <v>4264784.98292635</v>
       </c>
       <c r="P15">
-        <v>17.63691862922219</v>
+        <v>15.59192767257635</v>
       </c>
       <c r="Q15">
-        <v>0.02900106922098217</v>
+        <v>0.02595390433655549</v>
       </c>
       <c r="R15">
-        <v>29.90238194537063</v>
+        <v>30.00138527124204</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -3414,55 +3691,55 @@
         <v>1</v>
       </c>
       <c r="B16" t="s">
-        <v>156</v>
+        <v>193</v>
       </c>
       <c r="C16" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="D16" t="s">
-        <v>238</v>
+        <v>195</v>
       </c>
       <c r="E16" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F16">
-        <v>83.48009669833017</v>
+        <v>83.15986567265455</v>
       </c>
       <c r="G16">
         <v>650</v>
       </c>
       <c r="H16" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I16">
         <v>9.525</v>
       </c>
       <c r="J16" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K16">
         <v>4.71984827318464</v>
       </c>
       <c r="L16">
-        <v>3.95454545454546</v>
+        <v>15.08333333333334</v>
       </c>
       <c r="M16">
-        <v>2.457239863636367</v>
+        <v>9.372345916666671</v>
       </c>
       <c r="N16">
-        <v>4395076.944624769</v>
+        <v>4719848.27318464</v>
       </c>
       <c r="O16">
-        <v>4277208.149063417</v>
+        <v>4300284.718696806</v>
       </c>
       <c r="P16">
-        <v>14.57029511995486</v>
+        <v>15.44354501643771</v>
       </c>
       <c r="Q16">
-        <v>0.0239689416940633</v>
+        <v>0.02570105926302396</v>
       </c>
       <c r="R16">
-        <v>30.31176784233739</v>
+        <v>29.88013127540219</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -3470,55 +3747,55 @@
         <v>1</v>
       </c>
       <c r="B17" t="s">
-        <v>157</v>
+        <v>196</v>
       </c>
       <c r="C17" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="D17" t="s">
-        <v>239</v>
+        <v>197</v>
       </c>
       <c r="E17" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F17">
-        <v>83.35817215494843</v>
+        <v>83.15986567265404</v>
       </c>
       <c r="G17">
         <v>650</v>
       </c>
       <c r="H17" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I17">
         <v>9.525</v>
       </c>
       <c r="J17" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K17">
         <v>4.71984827318464</v>
       </c>
       <c r="L17">
-        <v>11.81818181818182</v>
+        <v>1.166666666666657</v>
       </c>
       <c r="M17">
-        <v>7.343475454545456</v>
+        <v>0.7249328333333274</v>
       </c>
       <c r="N17">
-        <v>4719848.27318464</v>
+        <v>4300284.718696806</v>
       </c>
       <c r="O17">
-        <v>4385310.742065813</v>
+        <v>4266152.899723101</v>
       </c>
       <c r="P17">
-        <v>14.58727711142327</v>
+        <v>15.56426219744285</v>
       </c>
       <c r="Q17">
-        <v>0.02398728953275086</v>
+        <v>0.02590762510693271</v>
       </c>
       <c r="R17">
-        <v>29.9356736769853</v>
+        <v>29.99668559798126</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -3526,55 +3803,55 @@
         <v>1</v>
       </c>
       <c r="B18" t="s">
-        <v>158</v>
+        <v>198</v>
       </c>
       <c r="C18" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D18" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E18" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F18">
-        <v>83.26718957556959</v>
+        <v>83.03871377582662</v>
       </c>
       <c r="G18">
         <v>650</v>
       </c>
       <c r="H18" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I18">
         <v>9.525</v>
       </c>
       <c r="J18" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K18">
         <v>4.71984827318464</v>
       </c>
       <c r="L18">
-        <v>0.3939393939393909</v>
+        <v>15.00000000000001</v>
       </c>
       <c r="M18">
-        <v>0.2447825151515133</v>
+        <v>9.320565000000007</v>
       </c>
       <c r="N18">
         <v>4719848.27318464</v>
       </c>
       <c r="O18">
-        <v>4709102.743059322</v>
+        <v>4303956.820596868</v>
       </c>
       <c r="P18">
-        <v>14.42576640305153</v>
+        <v>15.40818877450787</v>
       </c>
       <c r="Q18">
-        <v>0.02369330693116114</v>
+        <v>0.02564161812748711</v>
       </c>
       <c r="R18">
-        <v>28.88808041268108</v>
+        <v>29.86767246284327</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -3582,55 +3859,55 @@
         <v>1</v>
       </c>
       <c r="B19" t="s">
-        <v>159</v>
+        <v>201</v>
       </c>
       <c r="C19" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D19" t="s">
-        <v>240</v>
+        <v>202</v>
       </c>
       <c r="E19" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F19">
-        <v>83.26718957557077</v>
+        <v>83.0387137758272</v>
       </c>
       <c r="G19">
         <v>650</v>
       </c>
       <c r="H19" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I19">
         <v>9.525</v>
       </c>
       <c r="J19" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K19">
         <v>4.71984827318464</v>
       </c>
       <c r="L19">
-        <v>11.42424242424243</v>
+        <v>1.249999999999986</v>
       </c>
       <c r="M19">
-        <v>7.098692939393943</v>
+        <v>0.7767137499999913</v>
       </c>
       <c r="N19">
-        <v>4709102.743059322</v>
+        <v>4303956.820596868</v>
       </c>
       <c r="O19">
-        <v>4386051.382265373</v>
+        <v>4267512.091864506</v>
       </c>
       <c r="P19">
-        <v>14.46175418553516</v>
+        <v>15.53675112445274</v>
       </c>
       <c r="Q19">
-        <v>0.02378081490198043</v>
+        <v>0.02586160521201001</v>
       </c>
       <c r="R19">
-        <v>29.93314503204199</v>
+        <v>29.99201808634287</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -3638,7 +3915,7 @@
         <v>1</v>
       </c>
       <c r="B20" t="s">
-        <v>160</v>
+        <v>203</v>
       </c>
       <c r="C20" t="s">
         <v>204</v>
@@ -3647,46 +3924,46 @@
         <v>205</v>
       </c>
       <c r="E20" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F20">
-        <v>83.17651692061025</v>
+        <v>82.91812404016939</v>
       </c>
       <c r="G20">
         <v>650</v>
       </c>
       <c r="H20" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I20">
         <v>9.525</v>
       </c>
       <c r="J20" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K20">
         <v>4.71984827318464</v>
       </c>
       <c r="L20">
-        <v>4.742424242424242</v>
+        <v>15.41666666666669</v>
       </c>
       <c r="M20">
-        <v>2.946804893939394</v>
+        <v>9.579469583333347</v>
       </c>
       <c r="N20">
         <v>4719848.27318464</v>
       </c>
       <c r="O20">
-        <v>4589100.989462513</v>
+        <v>4293116.39393353</v>
       </c>
       <c r="P20">
-        <v>14.46489843093062</v>
+        <v>15.42377543212561</v>
       </c>
       <c r="Q20">
-        <v>0.02376824369340538</v>
+        <v>0.02566933545896386</v>
       </c>
       <c r="R20">
-        <v>29.26317776566481</v>
+        <v>29.90449716433881</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -3694,55 +3971,55 @@
         <v>1</v>
       </c>
       <c r="B21" t="s">
-        <v>161</v>
+        <v>206</v>
       </c>
       <c r="C21" t="s">
         <v>205</v>
       </c>
       <c r="D21" t="s">
-        <v>241</v>
+        <v>207</v>
       </c>
       <c r="E21" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F21">
-        <v>83.1765169206105</v>
+        <v>82.91812404016936</v>
       </c>
       <c r="G21">
         <v>650</v>
       </c>
       <c r="H21" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I21">
         <v>9.525</v>
       </c>
       <c r="J21" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K21">
         <v>4.71984827318464</v>
       </c>
       <c r="L21">
-        <v>7.075757575757578</v>
+        <v>0.8333333333333144</v>
       </c>
       <c r="M21">
-        <v>4.396670560606062</v>
+        <v>0.5178091666666549</v>
       </c>
       <c r="N21">
-        <v>4589100.989462513</v>
+        <v>4293116.39393353</v>
       </c>
       <c r="O21">
-        <v>4386785.729119765</v>
+        <v>4268862.652426816</v>
       </c>
       <c r="P21">
-        <v>14.4873872272926</v>
+        <v>15.50939295603778</v>
       </c>
       <c r="Q21">
-        <v>0.02382290116920245</v>
+        <v>0.0258158421275348</v>
       </c>
       <c r="R21">
-        <v>29.93063850595119</v>
+        <v>29.98738237326656</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -3750,55 +4027,55 @@
         <v>1</v>
       </c>
       <c r="B22" t="s">
-        <v>162</v>
+        <v>208</v>
       </c>
       <c r="C22" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D22" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="E22" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F22">
-        <v>83.08615160641925</v>
+        <v>82.79809193244293</v>
       </c>
       <c r="G22">
         <v>650</v>
       </c>
       <c r="H22" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I22">
         <v>9.525</v>
       </c>
       <c r="J22" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K22">
         <v>4.71984827318464</v>
       </c>
       <c r="L22">
-        <v>9.090909090909093</v>
+        <v>15.83333333333336</v>
       </c>
       <c r="M22">
-        <v>5.648827272727274</v>
+        <v>9.838374166666684</v>
       </c>
       <c r="N22">
         <v>4719848.27318464</v>
       </c>
       <c r="O22">
-        <v>4466409.140953656</v>
+        <v>4282310.285287289</v>
       </c>
       <c r="P22">
-        <v>14.50459488491807</v>
+        <v>15.43942228150298</v>
       </c>
       <c r="Q22">
-        <v>0.02384420282396576</v>
+        <v>0.02569715482119771</v>
       </c>
       <c r="R22">
-        <v>29.66254184797568</v>
+        <v>29.94134118304883</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -3806,55 +4083,55 @@
         <v>1</v>
       </c>
       <c r="B23" t="s">
-        <v>163</v>
+        <v>211</v>
       </c>
       <c r="C23" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D23" t="s">
-        <v>242</v>
+        <v>212</v>
       </c>
       <c r="E23" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F23">
-        <v>83.08615160641978</v>
+        <v>82.79809193243968</v>
       </c>
       <c r="G23">
         <v>650</v>
       </c>
       <c r="H23" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I23">
         <v>9.525</v>
       </c>
       <c r="J23" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K23">
         <v>4.71984827318464</v>
       </c>
       <c r="L23">
-        <v>2.727272727272734</v>
+        <v>0.416666666666643</v>
       </c>
       <c r="M23">
-        <v>1.694648181818186</v>
+        <v>0.2589045833333186</v>
       </c>
       <c r="N23">
-        <v>4466409.140953656</v>
+        <v>4282310.285287289</v>
       </c>
       <c r="O23">
-        <v>4387522.113075241</v>
+        <v>4270204.660352265</v>
       </c>
       <c r="P23">
-        <v>14.51334105865925</v>
+        <v>15.48218626105993</v>
       </c>
       <c r="Q23">
-        <v>0.02386551453217552</v>
+        <v>0.02577033344249054</v>
       </c>
       <c r="R23">
-        <v>29.92812565886573</v>
+        <v>29.98277814509681</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -3862,335 +4139,335 @@
         <v>1</v>
       </c>
       <c r="B24" t="s">
-        <v>164</v>
+        <v>213</v>
       </c>
       <c r="C24" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="D24" t="s">
-        <v>243</v>
+        <v>215</v>
       </c>
       <c r="E24" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F24">
-        <v>82.99609342415255</v>
+        <v>82.67861297029437</v>
       </c>
       <c r="G24">
         <v>650</v>
       </c>
       <c r="H24" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I24">
         <v>9.525</v>
       </c>
       <c r="J24" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K24">
         <v>4.71984827318464</v>
       </c>
       <c r="L24">
-        <v>11.81818181818181</v>
+        <v>16.25000000000003</v>
       </c>
       <c r="M24">
-        <v>7.343475454545449</v>
+        <v>10.09727875000002</v>
       </c>
       <c r="N24">
         <v>4719848.27318464</v>
       </c>
       <c r="O24">
-        <v>4388255.072674902</v>
+        <v>4271538.199802791</v>
       </c>
       <c r="P24">
-        <v>14.52391508409313</v>
+        <v>15.45512960495457</v>
       </c>
       <c r="Q24">
-        <v>0.02388283771964618</v>
+        <v>0.02572507673958841</v>
       </c>
       <c r="R24">
-        <v>29.92562512549114</v>
+        <v>29.97820507110624</v>
       </c>
     </row>
     <row r="25" spans="1:18">
       <c r="A25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B25" t="s">
-        <v>165</v>
+        <v>216</v>
       </c>
       <c r="C25" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="D25" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="E25" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F25">
-        <v>82.90634061755283</v>
+        <v>82.55968272326744</v>
       </c>
       <c r="G25">
         <v>650</v>
       </c>
       <c r="H25" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I25">
         <v>9.525</v>
       </c>
       <c r="J25" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K25">
         <v>4.71984827318464</v>
       </c>
       <c r="L25">
-        <v>2.121212121212125</v>
+        <v>16.66666666666667</v>
       </c>
       <c r="M25">
-        <v>1.318059696969699</v>
+        <v>10.35618333333334</v>
       </c>
       <c r="N25">
         <v>4719848.27318464</v>
       </c>
       <c r="O25">
-        <v>4662190.564484201</v>
+        <v>4260799.845747569</v>
       </c>
       <c r="P25">
-        <v>14.38488865675069</v>
+        <v>15.47089768764446</v>
       </c>
       <c r="Q25">
-        <v>0.02363030796836476</v>
+        <v>0.02575310174430352</v>
       </c>
       <c r="R25">
-        <v>29.03299059112346</v>
+        <v>30.01508938020371</v>
       </c>
     </row>
     <row r="26" spans="1:18">
       <c r="A26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B26" t="s">
-        <v>166</v>
+        <v>219</v>
       </c>
       <c r="C26" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="D26" t="s">
-        <v>244</v>
+        <v>220</v>
       </c>
       <c r="E26" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F26">
-        <v>82.90634061755314</v>
+        <v>82.55968272326763</v>
       </c>
       <c r="G26">
         <v>650</v>
       </c>
       <c r="H26" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I26">
         <v>9.525</v>
       </c>
       <c r="J26" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K26">
         <v>4.71984827318464</v>
       </c>
       <c r="L26">
-        <v>9.696969696969688</v>
+        <v>8.333333333333332</v>
       </c>
       <c r="M26">
-        <v>6.025415757575752</v>
+        <v>5.178091666666666</v>
       </c>
       <c r="N26">
-        <v>4662190.564484201</v>
+        <v>4260799.845747569</v>
       </c>
       <c r="O26">
-        <v>4388980.181271587</v>
+        <v>4012102.65652155</v>
       </c>
       <c r="P26">
-        <v>14.41542362352533</v>
+        <v>16.4069565158345</v>
       </c>
       <c r="Q26">
-        <v>0.02370437310878285</v>
+        <v>0.02735606299713765</v>
       </c>
       <c r="R26">
-        <v>29.92315199289171</v>
+        <v>30.90977882359325</v>
       </c>
     </row>
     <row r="27" spans="1:18">
       <c r="A27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B27" t="s">
-        <v>167</v>
+        <v>221</v>
       </c>
       <c r="C27" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="D27" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="E27" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F27">
-        <v>82.81689018430231</v>
+        <v>82.36499511695013</v>
       </c>
       <c r="G27">
         <v>650</v>
       </c>
       <c r="H27" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I27">
         <v>9.525</v>
       </c>
       <c r="J27" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K27">
         <v>4.71984827318464</v>
       </c>
       <c r="L27">
-        <v>6.969696969696983</v>
+        <v>8.333333333333336</v>
       </c>
       <c r="M27">
-        <v>4.330767575757585</v>
+        <v>5.178091666666668</v>
       </c>
       <c r="N27">
         <v>4719848.27318464</v>
       </c>
       <c r="O27">
-        <v>4528061.075637412</v>
+        <v>4497112.975992722</v>
       </c>
       <c r="P27">
-        <v>14.43056745954526</v>
+        <v>14.64108052367966</v>
       </c>
       <c r="Q27">
-        <v>0.02371713671083749</v>
+        <v>0.02433553867616207</v>
       </c>
       <c r="R27">
-        <v>29.45983396463809</v>
+        <v>29.23352039564656</v>
       </c>
     </row>
     <row r="28" spans="1:18">
       <c r="A28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B28" t="s">
-        <v>168</v>
+        <v>224</v>
       </c>
       <c r="C28" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="D28" t="s">
-        <v>245</v>
+        <v>225</v>
       </c>
       <c r="E28" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F28">
-        <v>82.81689018430197</v>
+        <v>82.36499511695027</v>
       </c>
       <c r="G28">
         <v>650</v>
       </c>
       <c r="H28" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I28">
         <v>9.525</v>
       </c>
       <c r="J28" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K28">
         <v>4.71984827318464</v>
       </c>
       <c r="L28">
-        <v>4.848484848484844</v>
+        <v>16.66666666666667</v>
       </c>
       <c r="M28">
-        <v>3.012707878787876</v>
+        <v>10.35618333333334</v>
       </c>
       <c r="N28">
-        <v>4528061.075637412</v>
+        <v>4497112.975992722</v>
       </c>
       <c r="O28">
-        <v>4389703.346438444</v>
+        <v>4015643.836980905</v>
       </c>
       <c r="P28">
-        <v>14.44598983331477</v>
+        <v>16.35417512029558</v>
       </c>
       <c r="Q28">
-        <v>0.02375457207462377</v>
+        <v>0.02726740596630698</v>
       </c>
       <c r="R28">
-        <v>29.92068609935606</v>
+        <v>30.89647085239977</v>
       </c>
     </row>
     <row r="29" spans="1:18">
       <c r="A29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B29" t="s">
-        <v>169</v>
+        <v>226</v>
       </c>
       <c r="C29" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="D29" t="s">
-        <v>246</v>
+        <v>228</v>
       </c>
       <c r="E29" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F29">
-        <v>82.72774080569728</v>
+        <v>82.17184041412425</v>
       </c>
       <c r="G29">
         <v>650</v>
       </c>
       <c r="H29" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I29">
         <v>9.525</v>
       </c>
       <c r="J29" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K29">
         <v>4.71984827318464</v>
       </c>
       <c r="L29">
-        <v>11.81818181818183</v>
+        <v>16.66666666666667</v>
       </c>
       <c r="M29">
-        <v>7.343475454545462</v>
+        <v>10.35618333333334</v>
       </c>
       <c r="N29">
         <v>4719848.27318464</v>
       </c>
       <c r="O29">
-        <v>4390427.943066845</v>
+        <v>4265228.172845608</v>
       </c>
       <c r="P29">
-        <v>14.47695467328054</v>
+        <v>15.38260031755399</v>
       </c>
       <c r="Q29">
-        <v>0.0238054261428331</v>
+        <v>0.02560539061813226</v>
       </c>
       <c r="R29">
-        <v>29.91821593606891</v>
+        <v>29.99986238716942</v>
       </c>
     </row>
     <row r="30" spans="1:18">
@@ -4198,55 +4475,55 @@
         <v>2</v>
       </c>
       <c r="B30" t="s">
-        <v>170</v>
+        <v>229</v>
       </c>
       <c r="C30" t="s">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="D30" t="s">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="E30" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F30">
-        <v>82.63889212201204</v>
+        <v>82.17184041412443</v>
       </c>
       <c r="G30">
         <v>650</v>
       </c>
       <c r="H30" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I30">
         <v>9.525</v>
       </c>
       <c r="J30" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K30">
         <v>4.71984827318464</v>
       </c>
       <c r="L30">
-        <v>16.66666666666667</v>
+        <v>8.333333333333329</v>
       </c>
       <c r="M30">
-        <v>10.35618333333334</v>
+        <v>5.178091666666663</v>
       </c>
       <c r="N30">
-        <v>4719848.27318464</v>
+        <v>4265228.172845608</v>
       </c>
       <c r="O30">
-        <v>4248945.751403102</v>
+        <v>4019144.629775605</v>
       </c>
       <c r="P30">
-        <v>14.52406541874561</v>
+        <v>16.30194855893287</v>
       </c>
       <c r="Q30">
-        <v>0.02389539425364393</v>
+        <v>0.02717968612876189</v>
       </c>
       <c r="R30">
-        <v>30.41245428616953</v>
+        <v>30.88333154209784</v>
       </c>
     </row>
     <row r="31" spans="1:18">
@@ -4254,55 +4531,55 @@
         <v>2</v>
       </c>
       <c r="B31" t="s">
-        <v>171</v>
+        <v>231</v>
       </c>
       <c r="C31" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="D31" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="E31" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F31">
-        <v>82.63889212201214</v>
+        <v>81.98019661524938</v>
       </c>
       <c r="G31">
         <v>650</v>
       </c>
       <c r="H31" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I31">
         <v>9.525</v>
       </c>
       <c r="J31" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K31">
         <v>4.71984827318464</v>
       </c>
       <c r="L31">
-        <v>8.333333333333336</v>
+        <v>8.333333333333343</v>
       </c>
       <c r="M31">
-        <v>5.178091666666668</v>
+        <v>5.178091666666672</v>
       </c>
       <c r="N31">
-        <v>4248945.751403102</v>
+        <v>4719848.27318464</v>
       </c>
       <c r="O31">
-        <v>3992706.601016642</v>
+        <v>4499192.658911228</v>
       </c>
       <c r="P31">
-        <v>14.55124049056735</v>
+        <v>14.56609032309931</v>
       </c>
       <c r="Q31">
-        <v>0.02396261231078147</v>
+        <v>0.02421058429454324</v>
       </c>
       <c r="R31">
-        <v>31.37405732844616</v>
+        <v>29.22691073316007</v>
       </c>
     </row>
     <row r="32" spans="1:18">
@@ -4310,87 +4587,87 @@
         <v>2</v>
       </c>
       <c r="B32" t="s">
-        <v>172</v>
+        <v>234</v>
       </c>
       <c r="C32" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="D32" t="s">
-        <v>217</v>
+        <v>235</v>
       </c>
       <c r="E32" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F32">
-        <v>82.43224668823387</v>
+        <v>81.98019661524933</v>
       </c>
       <c r="G32">
         <v>650</v>
       </c>
       <c r="H32" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I32">
         <v>9.525</v>
       </c>
       <c r="J32" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K32">
         <v>4.71984827318464</v>
       </c>
       <c r="L32">
-        <v>8.333333333333332</v>
+        <v>16.66666666666667</v>
       </c>
       <c r="M32">
-        <v>5.178091666666666</v>
+        <v>10.35618333333334</v>
       </c>
       <c r="N32">
-        <v>4719848.27318464</v>
+        <v>4499192.658911228</v>
       </c>
       <c r="O32">
-        <v>4491720.654554019</v>
+        <v>4022608.431624907</v>
       </c>
       <c r="P32">
-        <v>14.38081766129064</v>
+        <v>16.25025612447902</v>
       </c>
       <c r="Q32">
-        <v>0.0236385250201034</v>
+        <v>0.02709286817977086</v>
       </c>
       <c r="R32">
-        <v>29.57881401384673</v>
+        <v>30.8703475522066</v>
       </c>
     </row>
     <row r="33" spans="1:18">
       <c r="A33">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B33" t="s">
-        <v>173</v>
+        <v>236</v>
       </c>
       <c r="C33" t="s">
-        <v>217</v>
+        <v>237</v>
       </c>
       <c r="D33" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="E33" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F33">
-        <v>82.43224668823386</v>
+        <v>81.79004298848875</v>
       </c>
       <c r="G33">
         <v>650</v>
       </c>
       <c r="H33" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I33">
         <v>9.525</v>
       </c>
       <c r="J33" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K33">
         <v>4.71984827318464</v>
@@ -4402,219 +4679,219 @@
         <v>10.35618333333334</v>
       </c>
       <c r="N33">
-        <v>4491720.654554019</v>
+        <v>4719848.27318464</v>
       </c>
       <c r="O33">
-        <v>3996585.168007816</v>
+        <v>4269563.337796072</v>
       </c>
       <c r="P33">
-        <v>14.43398513069891</v>
+        <v>15.2959384396723</v>
       </c>
       <c r="Q33">
-        <v>0.02376918171064665</v>
+        <v>0.0254604260899656</v>
       </c>
       <c r="R33">
-        <v>31.35881307288549</v>
+        <v>29.98497816212387</v>
       </c>
     </row>
     <row r="34" spans="1:18">
       <c r="A34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B34" t="s">
-        <v>174</v>
+        <v>239</v>
       </c>
       <c r="C34" t="s">
-        <v>218</v>
+        <v>238</v>
       </c>
       <c r="D34" t="s">
-        <v>219</v>
+        <v>240</v>
       </c>
       <c r="E34" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F34">
-        <v>82.22735490824429</v>
+        <v>81.79004298848875</v>
       </c>
       <c r="G34">
         <v>650</v>
       </c>
       <c r="H34" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I34">
         <v>9.525</v>
       </c>
       <c r="J34" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K34">
         <v>4.71984827318464</v>
       </c>
       <c r="L34">
-        <v>16.66666666666666</v>
+        <v>8.333333333333332</v>
       </c>
       <c r="M34">
-        <v>10.35618333333333</v>
+        <v>5.178091666666666</v>
       </c>
       <c r="N34">
-        <v>4719848.27318464</v>
+        <v>4269563.337796072</v>
       </c>
       <c r="O34">
-        <v>4253773.090416066</v>
+        <v>4026033.715253451</v>
       </c>
       <c r="P34">
-        <v>14.45173635840214</v>
+        <v>16.19909697334661</v>
       </c>
       <c r="Q34">
-        <v>0.02377597088891475</v>
+        <v>0.02700695084199745</v>
       </c>
       <c r="R34">
-        <v>30.39518554510471</v>
+        <v>30.85752403773261</v>
       </c>
     </row>
     <row r="35" spans="1:18">
       <c r="A35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B35" t="s">
-        <v>175</v>
+        <v>241</v>
       </c>
       <c r="C35" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D35" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="E35" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F35">
-        <v>82.22735490824445</v>
+        <v>81.60135857225839</v>
       </c>
       <c r="G35">
         <v>650</v>
       </c>
       <c r="H35" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I35">
         <v>9.525</v>
       </c>
       <c r="J35" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K35">
         <v>4.71984827318464</v>
       </c>
       <c r="L35">
-        <v>8.333333333333343</v>
+        <v>8.333333333333336</v>
       </c>
       <c r="M35">
-        <v>5.178091666666672</v>
+        <v>5.178091666666668</v>
       </c>
       <c r="N35">
-        <v>4253773.090416066</v>
+        <v>4719848.27318464</v>
       </c>
       <c r="O35">
-        <v>4000409.836050834</v>
+        <v>4501229.973452239</v>
       </c>
       <c r="P35">
-        <v>14.4787760998358</v>
+        <v>14.49235990368231</v>
       </c>
       <c r="Q35">
-        <v>0.02384260752424487</v>
+        <v>0.02408773338602531</v>
       </c>
       <c r="R35">
-        <v>31.34380239990045</v>
+        <v>29.22044007144465</v>
       </c>
     </row>
     <row r="36" spans="1:18">
       <c r="A36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B36" t="s">
-        <v>176</v>
+        <v>244</v>
       </c>
       <c r="C36" t="s">
-        <v>220</v>
+        <v>243</v>
       </c>
       <c r="D36" t="s">
-        <v>221</v>
+        <v>245</v>
       </c>
       <c r="E36" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F36">
-        <v>82.02418913804641</v>
+        <v>81.60135857225833</v>
       </c>
       <c r="G36">
         <v>650</v>
       </c>
       <c r="H36" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I36">
         <v>9.525</v>
       </c>
       <c r="J36" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K36">
         <v>4.71984827318464</v>
       </c>
       <c r="L36">
-        <v>8.333333333333329</v>
+        <v>16.66666666666667</v>
       </c>
       <c r="M36">
-        <v>5.178091666666663</v>
+        <v>10.35618333333334</v>
       </c>
       <c r="N36">
-        <v>4719848.27318464</v>
+        <v>4501229.973452239</v>
       </c>
       <c r="O36">
-        <v>4493979.833443145</v>
+        <v>4029422.796164739</v>
       </c>
       <c r="P36">
-        <v>14.30962948602771</v>
+        <v>16.14845513716042</v>
       </c>
       <c r="Q36">
-        <v>0.02352131394351377</v>
+        <v>0.02692190692410061</v>
       </c>
       <c r="R36">
-        <v>29.57137530550629</v>
+        <v>30.84485177355788</v>
       </c>
     </row>
     <row r="37" spans="1:18">
       <c r="A37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B37" t="s">
-        <v>177</v>
+        <v>246</v>
       </c>
       <c r="C37" t="s">
-        <v>221</v>
+        <v>247</v>
       </c>
       <c r="D37" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E37" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F37">
-        <v>82.02418913804654</v>
+        <v>81.41412332765232</v>
       </c>
       <c r="G37">
         <v>650</v>
       </c>
       <c r="H37" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I37">
         <v>9.525</v>
       </c>
       <c r="J37" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K37">
         <v>4.71984827318464</v>
@@ -4626,19 +4903,19 @@
         <v>10.35618333333334</v>
       </c>
       <c r="N37">
-        <v>4493979.833443145</v>
+        <v>4719848.27318464</v>
       </c>
       <c r="O37">
-        <v>4004197.098644243</v>
+        <v>4273808.429490295</v>
       </c>
       <c r="P37">
-        <v>14.36253376489847</v>
+        <v>15.2108596894021</v>
       </c>
       <c r="Q37">
-        <v>0.02365086019015161</v>
+        <v>0.02531811995747342</v>
       </c>
       <c r="R37">
-        <v>31.32895975241713</v>
+        <v>29.9704246394195</v>
       </c>
     </row>
     <row r="38" spans="1:18">
@@ -4646,55 +4923,55 @@
         <v>3</v>
       </c>
       <c r="B38" t="s">
-        <v>178</v>
+        <v>249</v>
       </c>
       <c r="C38" t="s">
-        <v>222</v>
+        <v>248</v>
       </c>
       <c r="D38" t="s">
-        <v>223</v>
+        <v>250</v>
       </c>
       <c r="E38" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F38">
-        <v>81.82272724008702</v>
+        <v>81.41412332765235</v>
       </c>
       <c r="G38">
         <v>650</v>
       </c>
       <c r="H38" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I38">
         <v>9.525</v>
       </c>
       <c r="J38" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K38">
         <v>4.71984827318464</v>
       </c>
       <c r="L38">
-        <v>16.66666666666667</v>
+        <v>8.333333333333329</v>
       </c>
       <c r="M38">
-        <v>10.35618333333334</v>
+        <v>5.178091666666663</v>
       </c>
       <c r="N38">
-        <v>4719848.27318464</v>
+        <v>4273808.429490295</v>
       </c>
       <c r="O38">
-        <v>4258491.258129958</v>
+        <v>4032775.141727288</v>
       </c>
       <c r="P38">
-        <v>14.38062167412159</v>
+        <v>16.09832612448297</v>
       </c>
       <c r="Q38">
-        <v>0.02365855929589617</v>
+        <v>0.02683772889308898</v>
       </c>
       <c r="R38">
-        <v>30.37833573479849</v>
+        <v>30.83233221511762</v>
       </c>
     </row>
     <row r="39" spans="1:18">
@@ -4702,55 +4979,55 @@
         <v>3</v>
       </c>
       <c r="B39" t="s">
-        <v>179</v>
+        <v>251</v>
       </c>
       <c r="C39" t="s">
-        <v>223</v>
+        <v>252</v>
       </c>
       <c r="D39" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="E39" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F39">
-        <v>81.82272724008705</v>
+        <v>81.22831727508509</v>
       </c>
       <c r="G39">
         <v>650</v>
       </c>
       <c r="H39" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I39">
         <v>9.525</v>
       </c>
       <c r="J39" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K39">
         <v>4.71984827318464</v>
       </c>
       <c r="L39">
-        <v>8.333333333333336</v>
+        <v>8.333333333333343</v>
       </c>
       <c r="M39">
-        <v>5.178091666666668</v>
+        <v>5.178091666666672</v>
       </c>
       <c r="N39">
-        <v>4258491.258129958</v>
+        <v>4719848.27318464</v>
       </c>
       <c r="O39">
-        <v>4007932.971744596</v>
+        <v>4503226.28198659</v>
       </c>
       <c r="P39">
-        <v>14.40752835731037</v>
+        <v>14.41985222713381</v>
       </c>
       <c r="Q39">
-        <v>0.02372462867801883</v>
+        <v>0.02396692400550331</v>
       </c>
       <c r="R39">
-        <v>31.31433914466616</v>
+        <v>29.21410381484037</v>
       </c>
     </row>
     <row r="40" spans="1:18">
@@ -4758,335 +5035,55 @@
         <v>3</v>
       </c>
       <c r="B40" t="s">
-        <v>180</v>
+        <v>254</v>
       </c>
       <c r="C40" t="s">
-        <v>224</v>
+        <v>253</v>
       </c>
       <c r="D40" t="s">
-        <v>225</v>
+        <v>255</v>
       </c>
       <c r="E40" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F40">
-        <v>81.6229428664834</v>
+        <v>81.22831727508517</v>
       </c>
       <c r="G40">
         <v>650</v>
       </c>
       <c r="H40" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I40">
         <v>9.525</v>
       </c>
       <c r="J40" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K40">
         <v>4.71984827318464</v>
       </c>
       <c r="L40">
-        <v>8.333333333333332</v>
+        <v>16.66666666666667</v>
       </c>
       <c r="M40">
-        <v>5.178091666666666</v>
+        <v>10.35618333333334</v>
       </c>
       <c r="N40">
-        <v>4719848.27318464</v>
+        <v>4503226.28198659</v>
       </c>
       <c r="O40">
-        <v>4496189.582882936</v>
+        <v>4036092.034052541</v>
       </c>
       <c r="P40">
-        <v>14.23962958064549</v>
+        <v>16.04869842621639</v>
       </c>
       <c r="Q40">
-        <v>0.02340606226923772</v>
+        <v>0.02675439719162638</v>
       </c>
       <c r="R40">
-        <v>29.56410477825145</v>
-      </c>
-    </row>
-    <row r="41" spans="1:18">
-      <c r="A41">
-        <v>3</v>
-      </c>
-      <c r="B41" t="s">
-        <v>181</v>
-      </c>
-      <c r="C41" t="s">
-        <v>225</v>
-      </c>
-      <c r="D41" t="s">
-        <v>252</v>
-      </c>
-      <c r="E41" t="s">
-        <v>255</v>
-      </c>
-      <c r="F41">
-        <v>81.62294286648347</v>
-      </c>
-      <c r="G41">
-        <v>650</v>
-      </c>
-      <c r="H41" t="s">
-        <v>86</v>
-      </c>
-      <c r="I41">
-        <v>9.525</v>
-      </c>
-      <c r="J41" t="s">
-        <v>85</v>
-      </c>
-      <c r="K41">
-        <v>4.71984827318464</v>
-      </c>
-      <c r="L41">
-        <v>16.66666666666667</v>
-      </c>
-      <c r="M41">
-        <v>10.35618333333334</v>
-      </c>
-      <c r="N41">
-        <v>4496189.582882936</v>
-      </c>
-      <c r="O41">
-        <v>4011632.208642931</v>
-      </c>
-      <c r="P41">
-        <v>14.29227506214354</v>
-      </c>
-      <c r="Q41">
-        <v>0.02353452450087901</v>
-      </c>
-      <c r="R41">
-        <v>31.29988206599901</v>
-      </c>
-    </row>
-    <row r="42" spans="1:18">
-      <c r="A42">
-        <v>3</v>
-      </c>
-      <c r="B42" t="s">
-        <v>182</v>
-      </c>
-      <c r="C42" t="s">
-        <v>226</v>
-      </c>
-      <c r="D42" t="s">
-        <v>227</v>
-      </c>
-      <c r="E42" t="s">
-        <v>255</v>
-      </c>
-      <c r="F42">
-        <v>81.42481458511482</v>
-      </c>
-      <c r="G42">
-        <v>650</v>
-      </c>
-      <c r="H42" t="s">
-        <v>86</v>
-      </c>
-      <c r="I42">
-        <v>9.525</v>
-      </c>
-      <c r="J42" t="s">
-        <v>85</v>
-      </c>
-      <c r="K42">
-        <v>4.71984827318464</v>
-      </c>
-      <c r="L42">
-        <v>16.66666666666666</v>
-      </c>
-      <c r="M42">
-        <v>10.35618333333333</v>
-      </c>
-      <c r="N42">
-        <v>4719848.27318464</v>
-      </c>
-      <c r="O42">
-        <v>4263104.021114981</v>
-      </c>
-      <c r="P42">
-        <v>14.3106871761708</v>
-      </c>
-      <c r="Q42">
-        <v>0.02354310264541411</v>
-      </c>
-      <c r="R42">
-        <v>30.36188941331718</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18">
-      <c r="A43">
-        <v>3</v>
-      </c>
-      <c r="B43" t="s">
-        <v>183</v>
-      </c>
-      <c r="C43" t="s">
-        <v>227</v>
-      </c>
-      <c r="D43" t="s">
-        <v>253</v>
-      </c>
-      <c r="E43" t="s">
-        <v>255</v>
-      </c>
-      <c r="F43">
-        <v>81.42481458511494</v>
-      </c>
-      <c r="G43">
-        <v>650</v>
-      </c>
-      <c r="H43" t="s">
-        <v>86</v>
-      </c>
-      <c r="I43">
-        <v>9.525</v>
-      </c>
-      <c r="J43" t="s">
-        <v>85</v>
-      </c>
-      <c r="K43">
-        <v>4.71984827318464</v>
-      </c>
-      <c r="L43">
-        <v>8.333333333333343</v>
-      </c>
-      <c r="M43">
-        <v>5.178091666666672</v>
-      </c>
-      <c r="N43">
-        <v>4263104.021114981</v>
-      </c>
-      <c r="O43">
-        <v>4015282.442834999</v>
-      </c>
-      <c r="P43">
-        <v>14.33746300928767</v>
-      </c>
-      <c r="Q43">
-        <v>0.02360861840411159</v>
-      </c>
-      <c r="R43">
-        <v>31.28563610545507</v>
-      </c>
-    </row>
-    <row r="44" spans="1:18">
-      <c r="A44">
-        <v>3</v>
-      </c>
-      <c r="B44" t="s">
-        <v>184</v>
-      </c>
-      <c r="C44" t="s">
-        <v>228</v>
-      </c>
-      <c r="D44" t="s">
-        <v>229</v>
-      </c>
-      <c r="E44" t="s">
-        <v>255</v>
-      </c>
-      <c r="F44">
-        <v>81.22831727508505</v>
-      </c>
-      <c r="G44">
-        <v>650</v>
-      </c>
-      <c r="H44" t="s">
-        <v>86</v>
-      </c>
-      <c r="I44">
-        <v>9.525</v>
-      </c>
-      <c r="J44" t="s">
-        <v>85</v>
-      </c>
-      <c r="K44">
-        <v>4.71984827318464</v>
-      </c>
-      <c r="L44">
-        <v>8.333333333333329</v>
-      </c>
-      <c r="M44">
-        <v>5.178091666666663</v>
-      </c>
-      <c r="N44">
-        <v>4719848.27318464</v>
-      </c>
-      <c r="O44">
-        <v>4498351.552590257</v>
-      </c>
-      <c r="P44">
-        <v>14.1707846940583</v>
-      </c>
-      <c r="Q44">
-        <v>0.02329271508913296</v>
-      </c>
-      <c r="R44">
-        <v>29.55699664357599</v>
-      </c>
-    </row>
-    <row r="45" spans="1:18">
-      <c r="A45">
-        <v>3</v>
-      </c>
-      <c r="B45" t="s">
-        <v>185</v>
-      </c>
-      <c r="C45" t="s">
-        <v>229</v>
-      </c>
-      <c r="D45" t="s">
-        <v>254</v>
-      </c>
-      <c r="E45" t="s">
-        <v>255</v>
-      </c>
-      <c r="F45">
-        <v>81.22831727508517</v>
-      </c>
-      <c r="G45">
-        <v>650</v>
-      </c>
-      <c r="H45" t="s">
-        <v>86</v>
-      </c>
-      <c r="I45">
-        <v>9.525</v>
-      </c>
-      <c r="J45" t="s">
-        <v>85</v>
-      </c>
-      <c r="K45">
-        <v>4.71984827318464</v>
-      </c>
-      <c r="L45">
-        <v>16.66666666666667</v>
-      </c>
-      <c r="M45">
-        <v>10.35618333333334</v>
-      </c>
-      <c r="N45">
-        <v>4498351.552590257</v>
-      </c>
-      <c r="O45">
-        <v>4018896.773959124</v>
-      </c>
-      <c r="P45">
-        <v>14.22317564841557</v>
-      </c>
-      <c r="Q45">
-        <v>0.02342011875515169</v>
-      </c>
-      <c r="R45">
-        <v>31.27154941426402</v>
+        <v>30.81996005073758</v>
       </c>
     </row>
   </sheetData>
@@ -5096,62 +5093,62 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R25"/>
+  <dimension ref="A1:R20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="2" t="s">
+      <c r="A1" t="s">
         <v>256</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="F1" s="2" t="s">
+      <c r="C1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D1" t="s">
+        <v>144</v>
+      </c>
+      <c r="E1" t="s">
+        <v>145</v>
+      </c>
+      <c r="F1" t="s">
         <v>257</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" t="s">
         <v>258</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" t="s">
         <v>259</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" t="s">
         <v>260</v>
       </c>
-      <c r="J1" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="K1" s="2" t="s">
+      <c r="J1" t="s">
+        <v>115</v>
+      </c>
+      <c r="K1" t="s">
         <v>261</v>
       </c>
-      <c r="L1" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="M1" s="2" t="s">
+      <c r="L1" t="s">
+        <v>121</v>
+      </c>
+      <c r="M1" t="s">
         <v>262</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" t="s">
         <v>263</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" t="s">
         <v>264</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" t="s">
         <v>265</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" t="s">
         <v>266</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" t="s">
         <v>267</v>
       </c>
     </row>
@@ -5160,40 +5157,40 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="C2" t="s">
-        <v>230</v>
+        <v>162</v>
       </c>
       <c r="D2" t="s">
-        <v>187</v>
+        <v>164</v>
       </c>
       <c r="E2" t="s">
         <v>268</v>
       </c>
       <c r="F2">
-        <v>11.66666666666667</v>
+        <v>17.5</v>
       </c>
       <c r="G2">
-        <v>7.249328333333333</v>
+        <v>10.8739925</v>
       </c>
       <c r="H2">
-        <v>1.119677636567761</v>
+        <v>1.191852041253622</v>
       </c>
       <c r="I2">
-        <v>38.08569466312465</v>
+        <v>58.07194492013306</v>
       </c>
       <c r="J2">
-        <v>3.984783723618233</v>
+        <v>6.075880798904029</v>
       </c>
       <c r="K2">
-        <v>5343.674669046522</v>
+        <v>8147.877668946281</v>
       </c>
       <c r="L2">
         <v>0</v>
       </c>
       <c r="M2">
-        <v>3.984783723618233</v>
+        <v>6.075880798904029</v>
       </c>
       <c r="N2">
         <v>0.78</v>
@@ -5202,13 +5199,13 @@
         <v>0.357</v>
       </c>
       <c r="P2">
-        <v>12506675.77274331</v>
+        <v>15624217.33691421</v>
       </c>
       <c r="Q2">
         <v>0</v>
       </c>
       <c r="R2">
-        <v>12506675.77274331</v>
+        <v>15624217.33691421</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -5216,40 +5213,40 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="C3" t="s">
-        <v>231</v>
+        <v>167</v>
       </c>
       <c r="D3" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="E3" t="s">
         <v>268</v>
       </c>
       <c r="F3">
-        <v>23.33333333333333</v>
+        <v>35</v>
       </c>
       <c r="G3">
-        <v>14.49865666666667</v>
+        <v>21.747985</v>
       </c>
       <c r="H3">
-        <v>1.119214752767382</v>
+        <v>1.190603376636765</v>
       </c>
       <c r="I3">
-        <v>37.88678462044848</v>
+        <v>57.57111682998618</v>
       </c>
       <c r="J3">
-        <v>3.963972405680329</v>
+        <v>6.023480766828984</v>
       </c>
       <c r="K3">
-        <v>5315.766275465435</v>
+        <v>8077.608177933004</v>
       </c>
       <c r="L3">
         <v>0</v>
       </c>
       <c r="M3">
-        <v>3.963972405680329</v>
+        <v>6.023480766828984</v>
       </c>
       <c r="N3">
         <v>0.78</v>
@@ -5258,13 +5255,13 @@
         <v>0.357</v>
       </c>
       <c r="P3">
-        <v>12475993.31860835</v>
+        <v>15545258.93675933</v>
       </c>
       <c r="Q3">
         <v>0</v>
       </c>
       <c r="R3">
-        <v>12475993.31860835</v>
+        <v>15545258.93675933</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -5272,40 +5269,40 @@
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="C4" t="s">
-        <v>232</v>
+        <v>172</v>
       </c>
       <c r="D4" t="s">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="E4" t="s">
         <v>268</v>
       </c>
       <c r="F4">
-        <v>35</v>
+        <v>52.5</v>
       </c>
       <c r="G4">
-        <v>21.747985</v>
+        <v>32.6219775</v>
       </c>
       <c r="H4">
-        <v>1.118754294039912</v>
+        <v>1.189372346645897</v>
       </c>
       <c r="I4">
-        <v>37.68922567795127</v>
+        <v>57.07803641916518</v>
       </c>
       <c r="J4">
-        <v>3.943302449008111</v>
+        <v>5.971891349520104</v>
       </c>
       <c r="K4">
-        <v>5288.047450168857</v>
+        <v>8008.425737533449</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
       <c r="M4">
-        <v>3.943302449008111</v>
+        <v>5.971891349520104</v>
       </c>
       <c r="N4">
         <v>0.78</v>
@@ -5314,54 +5311,51 @@
         <v>0.357</v>
       </c>
       <c r="P4">
-        <v>12445525.99409463</v>
+        <v>15467564.03912066</v>
       </c>
       <c r="Q4">
         <v>0</v>
       </c>
       <c r="R4">
-        <v>12445525.99409463</v>
+        <v>15467564.03912066</v>
       </c>
     </row>
     <row r="5" spans="1:18">
-      <c r="A5">
-        <v>0</v>
-      </c>
       <c r="B5" t="s">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="C5" t="s">
-        <v>233</v>
+        <v>177</v>
       </c>
       <c r="D5" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="E5" t="s">
-        <v>268</v>
+        <v>160</v>
       </c>
       <c r="F5">
-        <v>46.66666666666666</v>
+        <v>70</v>
       </c>
       <c r="G5">
-        <v>28.99731333333333</v>
+        <v>43.49597</v>
       </c>
       <c r="H5">
-        <v>1.118296843425112</v>
+        <v>1.188158843482567</v>
       </c>
       <c r="I5">
-        <v>37.49320512744882</v>
+        <v>56.5926102456586</v>
       </c>
       <c r="J5">
-        <v>3.92279344934181</v>
+        <v>5.921102770440302</v>
       </c>
       <c r="K5">
-        <v>5260.544471436354</v>
+        <v>7940.317237215854</v>
       </c>
       <c r="L5">
         <v>0</v>
       </c>
       <c r="M5">
-        <v>3.92279344934181</v>
+        <v>12.5</v>
       </c>
       <c r="N5">
         <v>0.78</v>
@@ -5370,54 +5364,54 @@
         <v>0.357</v>
       </c>
       <c r="P5">
-        <v>12415302.53629384</v>
+        <v>0</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>16916025.69007904</v>
       </c>
       <c r="R5">
-        <v>12415302.53629384</v>
+        <v>16916025.69007904</v>
       </c>
     </row>
     <row r="6" spans="1:18">
       <c r="A6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="C6" t="s">
-        <v>234</v>
+        <v>182</v>
       </c>
       <c r="D6" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="E6" t="s">
         <v>268</v>
       </c>
       <c r="F6">
-        <v>58.33333333333333</v>
+        <v>86.25</v>
       </c>
       <c r="G6">
-        <v>36.24664166666666</v>
+        <v>53.59324875</v>
       </c>
       <c r="H6">
-        <v>1.117842207291969</v>
+        <v>1.170031541129076</v>
       </c>
       <c r="I6">
-        <v>37.29866131269092</v>
+        <v>51.32856045869275</v>
       </c>
       <c r="J6">
-        <v>3.902438955786296</v>
+        <v>5.370342173923548</v>
       </c>
       <c r="K6">
-        <v>5233.248688488538</v>
+        <v>7201.736262074955</v>
       </c>
       <c r="L6">
         <v>0</v>
       </c>
       <c r="M6">
-        <v>3.902438955786296</v>
+        <v>5.370342173923548</v>
       </c>
       <c r="N6">
         <v>0.78</v>
@@ -5426,51 +5420,54 @@
         <v>0.357</v>
       </c>
       <c r="P6">
-        <v>12385313.28662439</v>
+        <v>14564695.19587668</v>
       </c>
       <c r="Q6">
         <v>0</v>
       </c>
       <c r="R6">
-        <v>12385313.28662439</v>
+        <v>14564695.19587668</v>
       </c>
     </row>
     <row r="7" spans="1:18">
+      <c r="A7">
+        <v>1</v>
+      </c>
       <c r="B7" t="s">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="C7" t="s">
-        <v>235</v>
+        <v>187</v>
       </c>
       <c r="D7" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="E7" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="F7">
-        <v>70</v>
+        <v>102.5</v>
       </c>
       <c r="G7">
-        <v>43.49597</v>
+        <v>63.6905275</v>
       </c>
       <c r="H7">
-        <v>1.117389777288808</v>
+        <v>1.164965710386294</v>
       </c>
       <c r="I7">
-        <v>37.10540968692987</v>
+        <v>41.08115079386256</v>
       </c>
       <c r="J7">
-        <v>3.88221965980898</v>
+        <v>4.298188663193453</v>
       </c>
       <c r="K7">
-        <v>5206.134208197038</v>
+        <v>5763.956961115684</v>
       </c>
       <c r="L7">
         <v>0</v>
       </c>
       <c r="M7">
-        <v>12.5</v>
+        <v>4.298188663193453</v>
       </c>
       <c r="N7">
         <v>0.78</v>
@@ -5479,13 +5476,13 @@
         <v>0.357</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>12969554.36951518</v>
       </c>
       <c r="Q7">
-        <v>16916025.69007904</v>
+        <v>0</v>
       </c>
       <c r="R7">
-        <v>16916025.69007904</v>
+        <v>12969554.36951518</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -5493,40 +5490,40 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="C8" t="s">
-        <v>236</v>
+        <v>192</v>
       </c>
       <c r="D8" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E8" t="s">
         <v>268</v>
       </c>
       <c r="F8">
-        <v>81.81818181818181</v>
+        <v>118.75</v>
       </c>
       <c r="G8">
-        <v>50.83944545454546</v>
+        <v>73.78780625</v>
       </c>
       <c r="H8">
-        <v>1.118742777403476</v>
+        <v>1.1067025165583</v>
       </c>
       <c r="I8">
-        <v>37.4376201062648</v>
+        <v>27.05996016732582</v>
       </c>
       <c r="J8">
-        <v>3.916977767373811</v>
+        <v>2.831196589435429</v>
       </c>
       <c r="K8">
-        <v>5252.745525603627</v>
+        <v>3796.691250364699</v>
       </c>
       <c r="L8">
         <v>0</v>
       </c>
       <c r="M8">
-        <v>3.916977767373811</v>
+        <v>2.831196589435429</v>
       </c>
       <c r="N8">
         <v>0.78</v>
@@ -5535,13 +5532,13 @@
         <v>0.357</v>
       </c>
       <c r="P8">
-        <v>12406733.35113453</v>
+        <v>10816163.45383709</v>
       </c>
       <c r="Q8">
         <v>0</v>
       </c>
       <c r="R8">
-        <v>12406733.35113453</v>
+        <v>10816163.45383709</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -5549,10 +5546,10 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="C9" t="s">
-        <v>237</v>
+        <v>197</v>
       </c>
       <c r="D9" t="s">
         <v>199</v>
@@ -5561,28 +5558,28 @@
         <v>268</v>
       </c>
       <c r="F9">
-        <v>93.63636363636364</v>
+        <v>135</v>
       </c>
       <c r="G9">
-        <v>58.18292090909091</v>
+        <v>83.885085</v>
       </c>
       <c r="H9">
-        <v>1.118287671728371</v>
+        <v>1.106347658915597</v>
       </c>
       <c r="I9">
-        <v>37.24357876346446</v>
+        <v>26.93396281725086</v>
       </c>
       <c r="J9">
-        <v>3.896675845842932</v>
+        <v>2.818013891988561</v>
       </c>
       <c r="K9">
-        <v>5225.520242792289</v>
+        <v>3779.0129894345</v>
       </c>
       <c r="L9">
         <v>0</v>
       </c>
       <c r="M9">
-        <v>3.896675845842932</v>
+        <v>2.818013891988561</v>
       </c>
       <c r="N9">
         <v>0.78</v>
@@ -5591,13 +5588,13 @@
         <v>0.357</v>
       </c>
       <c r="P9">
-        <v>12376823.40030325</v>
+        <v>10796965.52906065</v>
       </c>
       <c r="Q9">
         <v>0</v>
       </c>
       <c r="R9">
-        <v>12376823.40030325</v>
+        <v>10796965.52906065</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -5605,40 +5602,40 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="C10" t="s">
-        <v>238</v>
+        <v>202</v>
       </c>
       <c r="D10" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E10" t="s">
         <v>268</v>
       </c>
       <c r="F10">
-        <v>105.4545454545455</v>
+        <v>151.25</v>
       </c>
       <c r="G10">
-        <v>65.52639636363637</v>
+        <v>93.98236375</v>
       </c>
       <c r="H10">
-        <v>1.103488095200171</v>
+        <v>1.105995289897938</v>
       </c>
       <c r="I10">
-        <v>27.10573423892676</v>
+        <v>26.80898559061113</v>
       </c>
       <c r="J10">
-        <v>2.835985783307106</v>
+        <v>2.804937926775326</v>
       </c>
       <c r="K10">
-        <v>3803.113655130495</v>
+        <v>3761.477858564248</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
       <c r="M10">
-        <v>2.835985783307106</v>
+        <v>2.804937926775326</v>
       </c>
       <c r="N10">
         <v>0.78</v>
@@ -5647,13 +5644,13 @@
         <v>0.357</v>
       </c>
       <c r="P10">
-        <v>10823138.61767111</v>
+        <v>10777925.72858675</v>
       </c>
       <c r="Q10">
         <v>0</v>
       </c>
       <c r="R10">
-        <v>10823138.61767111</v>
+        <v>10777925.72858675</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -5661,40 +5658,40 @@
         <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="C11" t="s">
-        <v>239</v>
+        <v>207</v>
       </c>
       <c r="D11" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="E11" t="s">
         <v>268</v>
       </c>
       <c r="F11">
-        <v>117.2727272727273</v>
+        <v>167.5</v>
       </c>
       <c r="G11">
-        <v>72.86987181818182</v>
+        <v>104.0796425</v>
       </c>
       <c r="H11">
-        <v>1.076285935204043</v>
+        <v>1.105645380860741</v>
       </c>
       <c r="I11">
-        <v>20.22685136732043</v>
+        <v>26.68501617413599</v>
       </c>
       <c r="J11">
-        <v>2.116270395524172</v>
+        <v>2.791967405497823</v>
       </c>
       <c r="K11">
-        <v>2837.960925805825</v>
+        <v>3744.08413012069</v>
       </c>
       <c r="L11">
         <v>0</v>
       </c>
       <c r="M11">
-        <v>2.116270395524172</v>
+        <v>2.791967405497823</v>
       </c>
       <c r="N11">
         <v>0.78</v>
@@ -5703,13 +5700,13 @@
         <v>0.357</v>
       </c>
       <c r="P11">
-        <v>9953691.026075777</v>
+        <v>10759042.11131523</v>
       </c>
       <c r="Q11">
         <v>0</v>
       </c>
       <c r="R11">
-        <v>9953691.026075777</v>
+        <v>10759042.11131523</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -5717,40 +5714,40 @@
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="C12" t="s">
-        <v>240</v>
+        <v>212</v>
       </c>
       <c r="D12" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="E12" t="s">
         <v>268</v>
       </c>
       <c r="F12">
-        <v>129.0909090909091</v>
+        <v>183.75</v>
       </c>
       <c r="G12">
-        <v>80.21334727272728</v>
+        <v>114.17692125</v>
       </c>
       <c r="H12">
-        <v>1.076104190723562</v>
+        <v>1.105297906914673</v>
       </c>
       <c r="I12">
-        <v>20.15795031849139</v>
+        <v>26.56204325486512</v>
       </c>
       <c r="J12">
-        <v>2.109061500416896</v>
+        <v>2.779101144517401</v>
       </c>
       <c r="K12">
-        <v>2828.293653289066</v>
+        <v>3726.830216820725</v>
       </c>
       <c r="L12">
         <v>0</v>
       </c>
       <c r="M12">
-        <v>2.109061500416896</v>
+        <v>2.779101144517401</v>
       </c>
       <c r="N12">
         <v>0.78</v>
@@ -5759,54 +5756,51 @@
         <v>0.357</v>
       </c>
       <c r="P12">
-        <v>9953691.026075777</v>
+        <v>10740312.89006076</v>
       </c>
       <c r="Q12">
         <v>0</v>
       </c>
       <c r="R12">
-        <v>9953691.026075777</v>
+        <v>10740312.89006076</v>
       </c>
     </row>
     <row r="13" spans="1:18">
-      <c r="A13">
-        <v>1</v>
-      </c>
       <c r="B13" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="C13" t="s">
-        <v>241</v>
+        <v>215</v>
       </c>
       <c r="D13" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="E13" t="s">
-        <v>268</v>
+        <v>160</v>
       </c>
       <c r="F13">
-        <v>140.9090909090909</v>
+        <v>200</v>
       </c>
       <c r="G13">
-        <v>87.55682272727275</v>
+        <v>124.2742</v>
       </c>
       <c r="H13">
-        <v>1.075924051146147</v>
+        <v>1.104952841906587</v>
       </c>
       <c r="I13">
-        <v>20.0896236552629</v>
+        <v>26.44005529537746</v>
       </c>
       <c r="J13">
-        <v>2.1019127014274</v>
+        <v>2.76633793671081</v>
       </c>
       <c r="K13">
-        <v>2818.706970868172</v>
+        <v>3709.714499887931</v>
       </c>
       <c r="L13">
         <v>0</v>
       </c>
       <c r="M13">
-        <v>2.1019127014274</v>
+        <v>12.5</v>
       </c>
       <c r="N13">
         <v>0.78</v>
@@ -5815,54 +5809,54 @@
         <v>0.357</v>
       </c>
       <c r="P13">
-        <v>9953691.026075777</v>
+        <v>0</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>16916025.69007904</v>
       </c>
       <c r="R13">
-        <v>9953691.026075777</v>
+        <v>16916025.69007904</v>
       </c>
     </row>
     <row r="14" spans="1:18">
       <c r="A14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B14" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="C14" t="s">
-        <v>242</v>
+        <v>220</v>
       </c>
       <c r="D14" t="s">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="E14" t="s">
         <v>268</v>
       </c>
       <c r="F14">
-        <v>152.7272727272727</v>
+        <v>225</v>
       </c>
       <c r="G14">
-        <v>94.9002981818182</v>
+        <v>139.808475</v>
       </c>
       <c r="H14">
-        <v>1.075743472407589</v>
+        <v>1.176402668937863</v>
       </c>
       <c r="I14">
-        <v>20.02134342154093</v>
+        <v>43.28210194660938</v>
       </c>
       <c r="J14">
-        <v>2.094768760207821</v>
+        <v>4.528467102579145</v>
       </c>
       <c r="K14">
-        <v>2809.126802813892</v>
+        <v>6072.764953900685</v>
       </c>
       <c r="L14">
         <v>0</v>
       </c>
       <c r="M14">
-        <v>2.094768760207821</v>
+        <v>4.528467102579145</v>
       </c>
       <c r="N14">
         <v>0.78</v>
@@ -5871,54 +5865,54 @@
         <v>0.357</v>
       </c>
       <c r="P14">
-        <v>9953691.026075777</v>
+        <v>13310641.584289</v>
       </c>
       <c r="Q14">
         <v>0</v>
       </c>
       <c r="R14">
-        <v>9953691.026075777</v>
+        <v>13310641.584289</v>
       </c>
     </row>
     <row r="15" spans="1:18">
       <c r="A15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B15" t="s">
-        <v>115</v>
+        <v>135</v>
       </c>
       <c r="C15" t="s">
-        <v>243</v>
+        <v>225</v>
       </c>
       <c r="D15" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="E15" t="s">
         <v>268</v>
       </c>
       <c r="F15">
-        <v>164.5454545454546</v>
+        <v>250</v>
       </c>
       <c r="G15">
-        <v>102.2437736363636</v>
+        <v>155.34275</v>
       </c>
       <c r="H15">
-        <v>1.075563793584955</v>
+        <v>1.175365262655659</v>
       </c>
       <c r="I15">
-        <v>19.95345363131741</v>
+        <v>42.94131350894822</v>
       </c>
       <c r="J15">
-        <v>2.087665669835559</v>
+        <v>4.492811504549465</v>
       </c>
       <c r="K15">
-        <v>2799.601416562882</v>
+        <v>6024.950083830923</v>
       </c>
       <c r="L15">
         <v>0</v>
       </c>
       <c r="M15">
-        <v>2.087665669835559</v>
+        <v>4.492811504549465</v>
       </c>
       <c r="N15">
         <v>0.78</v>
@@ -5927,54 +5921,54 @@
         <v>0.357</v>
       </c>
       <c r="P15">
-        <v>9953691.026075777</v>
+        <v>13257774.32459174</v>
       </c>
       <c r="Q15">
         <v>0</v>
       </c>
       <c r="R15">
-        <v>9953691.026075777</v>
+        <v>13257774.32459174</v>
       </c>
     </row>
     <row r="16" spans="1:18">
       <c r="A16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B16" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="C16" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
       <c r="D16" t="s">
-        <v>211</v>
+        <v>232</v>
       </c>
       <c r="E16" t="s">
         <v>268</v>
       </c>
       <c r="F16">
-        <v>176.3636363636364</v>
+        <v>275</v>
       </c>
       <c r="G16">
-        <v>109.5872490909091</v>
+        <v>170.877025</v>
       </c>
       <c r="H16">
-        <v>1.075386098420976</v>
+        <v>1.174341485055779</v>
       </c>
       <c r="I16">
-        <v>19.88623130338864</v>
+        <v>42.60541591342052</v>
       </c>
       <c r="J16">
-        <v>2.080632413896195</v>
+        <v>4.457667619600001</v>
       </c>
       <c r="K16">
-        <v>2790.169679683076</v>
+        <v>5977.821431235994</v>
       </c>
       <c r="L16">
         <v>0</v>
       </c>
       <c r="M16">
-        <v>2.080632413896195</v>
+        <v>4.457667619600001</v>
       </c>
       <c r="N16">
         <v>0.78</v>
@@ -5983,54 +5977,51 @@
         <v>0.357</v>
       </c>
       <c r="P16">
-        <v>9953691.026075777</v>
+        <v>13205685.28860052</v>
       </c>
       <c r="Q16">
         <v>0</v>
       </c>
       <c r="R16">
-        <v>9953691.026075777</v>
+        <v>13205685.28860052</v>
       </c>
     </row>
     <row r="17" spans="1:18">
-      <c r="A17">
-        <v>1</v>
-      </c>
       <c r="B17" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="C17" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="D17" t="s">
-        <v>213</v>
+        <v>237</v>
       </c>
       <c r="E17" t="s">
-        <v>268</v>
+        <v>160</v>
       </c>
       <c r="F17">
-        <v>188.1818181818182</v>
+        <v>300</v>
       </c>
       <c r="G17">
-        <v>116.9307245454546</v>
+        <v>186.4113</v>
       </c>
       <c r="H17">
-        <v>1.075208937983032</v>
+        <v>1.173330278949892</v>
       </c>
       <c r="I17">
-        <v>19.81930214378559</v>
+        <v>42.27412732967593</v>
       </c>
       <c r="J17">
-        <v>2.073629831215724</v>
+        <v>4.423005960727749</v>
       </c>
       <c r="K17">
-        <v>2780.77907625691</v>
+        <v>5931.339453455125</v>
       </c>
       <c r="L17">
         <v>0</v>
       </c>
       <c r="M17">
-        <v>2.073629831215724</v>
+        <v>12.5</v>
       </c>
       <c r="N17">
         <v>0.78</v>
@@ -6039,51 +6030,54 @@
         <v>0.357</v>
       </c>
       <c r="P17">
-        <v>9953691.026075777</v>
+        <v>0</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>16916025.69007904</v>
       </c>
       <c r="R17">
-        <v>9953691.026075777</v>
+        <v>16916025.69007904</v>
       </c>
     </row>
     <row r="18" spans="1:18">
+      <c r="A18">
+        <v>3</v>
+      </c>
       <c r="B18" t="s">
-        <v>118</v>
+        <v>138</v>
       </c>
       <c r="C18" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="D18" t="s">
-        <v>214</v>
+        <v>242</v>
       </c>
       <c r="E18" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="F18">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="G18">
-        <v>124.2742</v>
+        <v>201.945575</v>
       </c>
       <c r="H18">
-        <v>1.075031485401782</v>
+        <v>1.172332028741471</v>
       </c>
       <c r="I18">
-        <v>19.7524529569708</v>
+        <v>41.94749883413785</v>
       </c>
       <c r="J18">
-        <v>2.066635615830844</v>
+        <v>4.388831871894594</v>
       </c>
       <c r="K18">
-        <v>2771.399693541478</v>
+        <v>5885.511316848089</v>
       </c>
       <c r="L18">
         <v>0</v>
       </c>
       <c r="M18">
-        <v>12.5</v>
+        <v>4.388831871894594</v>
       </c>
       <c r="N18">
         <v>0.78</v>
@@ -6092,54 +6086,54 @@
         <v>0.357</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>13103715.43741976</v>
       </c>
       <c r="Q18">
-        <v>16916025.69007904</v>
+        <v>0</v>
       </c>
       <c r="R18">
-        <v>16916025.69007904</v>
+        <v>13103715.43741976</v>
       </c>
     </row>
     <row r="19" spans="1:18">
       <c r="A19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B19" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="C19" t="s">
+        <v>245</v>
+      </c>
+      <c r="D19" t="s">
         <v>247</v>
-      </c>
-      <c r="D19" t="s">
-        <v>216</v>
       </c>
       <c r="E19" t="s">
         <v>268</v>
       </c>
       <c r="F19">
-        <v>225</v>
+        <v>350</v>
       </c>
       <c r="G19">
-        <v>139.808475</v>
+        <v>217.47985</v>
       </c>
       <c r="H19">
-        <v>1.182117481906346</v>
+        <v>1.171345999649642</v>
       </c>
       <c r="I19">
-        <v>45.94051414351117</v>
+        <v>41.62532530102022</v>
       </c>
       <c r="J19">
-        <v>4.80660821951508</v>
+        <v>4.355123891449361</v>
       </c>
       <c r="K19">
-        <v>6445.757754534112</v>
+        <v>5840.308240911422</v>
       </c>
       <c r="L19">
         <v>0</v>
       </c>
       <c r="M19">
-        <v>4.80660821951508</v>
+        <v>4.355123891449361</v>
       </c>
       <c r="N19">
         <v>0.78</v>
@@ -6148,54 +6142,54 @@
         <v>0.357</v>
       </c>
       <c r="P19">
-        <v>13723730.8144163</v>
+        <v>13053809.19711511</v>
       </c>
       <c r="Q19">
         <v>0</v>
       </c>
       <c r="R19">
-        <v>13723730.8144163</v>
+        <v>13053809.19711511</v>
       </c>
     </row>
     <row r="20" spans="1:18">
       <c r="A20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B20" t="s">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="C20" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D20" t="s">
-        <v>218</v>
+        <v>252</v>
       </c>
       <c r="E20" t="s">
         <v>268</v>
       </c>
       <c r="F20">
-        <v>250</v>
+        <v>375</v>
       </c>
       <c r="G20">
-        <v>155.34275</v>
+        <v>233.014125</v>
       </c>
       <c r="H20">
-        <v>1.180970272062875</v>
+        <v>1.17037228888568</v>
       </c>
       <c r="I20">
-        <v>45.55064945980518</v>
+        <v>41.30759354245797</v>
       </c>
       <c r="J20">
-        <v>4.765817931723653</v>
+        <v>4.321880639588149</v>
       </c>
       <c r="K20">
-        <v>6391.057162800053</v>
+        <v>5795.728375300499</v>
       </c>
       <c r="L20">
         <v>0</v>
       </c>
       <c r="M20">
-        <v>4.765817931723653</v>
+        <v>4.321880639588149</v>
       </c>
       <c r="N20">
         <v>0.78</v>
@@ -6204,290 +6198,13 @@
         <v>0.357</v>
       </c>
       <c r="P20">
-        <v>13663074.09012518</v>
+        <v>13004608.44899116</v>
       </c>
       <c r="Q20">
         <v>0</v>
       </c>
       <c r="R20">
-        <v>13663074.09012518</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18">
-      <c r="A21">
-        <v>2</v>
-      </c>
-      <c r="B21" t="s">
-        <v>121</v>
-      </c>
-      <c r="C21" t="s">
-        <v>249</v>
-      </c>
-      <c r="D21" t="s">
-        <v>220</v>
-      </c>
-      <c r="E21" t="s">
-        <v>268</v>
-      </c>
-      <c r="F21">
-        <v>275.0000000000001</v>
-      </c>
-      <c r="G21">
-        <v>170.877025</v>
-      </c>
-      <c r="H21">
-        <v>1.179841182933404</v>
-      </c>
-      <c r="I21">
-        <v>45.16693046928879</v>
-      </c>
-      <c r="J21">
-        <v>4.725670648042011</v>
-      </c>
-      <c r="K21">
-        <v>6337.218852437298</v>
-      </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21">
-        <v>4.725670648042011</v>
-      </c>
-      <c r="N21">
-        <v>0.78</v>
-      </c>
-      <c r="O21">
-        <v>0.357</v>
-      </c>
-      <c r="P21">
-        <v>13603398.99923224</v>
-      </c>
-      <c r="Q21">
-        <v>0</v>
-      </c>
-      <c r="R21">
-        <v>13603398.99923224</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18">
-      <c r="B22" t="s">
-        <v>122</v>
-      </c>
-      <c r="C22" t="s">
-        <v>250</v>
-      </c>
-      <c r="D22" t="s">
-        <v>222</v>
-      </c>
-      <c r="E22" t="s">
-        <v>255</v>
-      </c>
-      <c r="F22">
-        <v>300.0000000000001</v>
-      </c>
-      <c r="G22">
-        <v>186.4113</v>
-      </c>
-      <c r="H22">
-        <v>1.178725261746657</v>
-      </c>
-      <c r="I22">
-        <v>44.78813300331705</v>
-      </c>
-      <c r="J22">
-        <v>4.686038287642569</v>
-      </c>
-      <c r="K22">
-        <v>6284.071064494438</v>
-      </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22">
-        <v>12.5</v>
-      </c>
-      <c r="N22">
-        <v>0.78</v>
-      </c>
-      <c r="O22">
-        <v>0.357</v>
-      </c>
-      <c r="P22">
-        <v>0</v>
-      </c>
-      <c r="Q22">
-        <v>16916025.69007904</v>
-      </c>
-      <c r="R22">
-        <v>16916025.69007904</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18">
-      <c r="A23">
-        <v>3</v>
-      </c>
-      <c r="B23" t="s">
-        <v>123</v>
-      </c>
-      <c r="C23" t="s">
-        <v>251</v>
-      </c>
-      <c r="D23" t="s">
-        <v>224</v>
-      </c>
-      <c r="E23" t="s">
-        <v>268</v>
-      </c>
-      <c r="F23">
-        <v>325.0000000000001</v>
-      </c>
-      <c r="G23">
-        <v>201.945575</v>
-      </c>
-      <c r="H23">
-        <v>1.177626548761907</v>
-      </c>
-      <c r="I23">
-        <v>44.41519308402132</v>
-      </c>
-      <c r="J23">
-        <v>4.647018783510063</v>
-      </c>
-      <c r="K23">
-        <v>6231.745129062665</v>
-      </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-      <c r="M23">
-        <v>4.647018783510063</v>
-      </c>
-      <c r="N23">
-        <v>0.78</v>
-      </c>
-      <c r="O23">
-        <v>0.357</v>
-      </c>
-      <c r="P23">
-        <v>13486563.75308981</v>
-      </c>
-      <c r="Q23">
-        <v>0</v>
-      </c>
-      <c r="R23">
-        <v>13486563.75308981</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18">
-      <c r="A24">
-        <v>3</v>
-      </c>
-      <c r="B24" t="s">
-        <v>124</v>
-      </c>
-      <c r="C24" t="s">
-        <v>252</v>
-      </c>
-      <c r="D24" t="s">
-        <v>226</v>
-      </c>
-      <c r="E24" t="s">
-        <v>268</v>
-      </c>
-      <c r="F24">
-        <v>350.0000000000001</v>
-      </c>
-      <c r="G24">
-        <v>217.47985</v>
-      </c>
-      <c r="H24">
-        <v>1.17654062678425</v>
-      </c>
-      <c r="I24">
-        <v>44.04701786062734</v>
-      </c>
-      <c r="J24">
-        <v>4.608497794183321</v>
-      </c>
-      <c r="K24">
-        <v>6180.087711955716</v>
-      </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
-      <c r="M24">
-        <v>4.608497794183321</v>
-      </c>
-      <c r="N24">
-        <v>0.78</v>
-      </c>
-      <c r="O24">
-        <v>0.357</v>
-      </c>
-      <c r="P24">
-        <v>13429377.21872473</v>
-      </c>
-      <c r="Q24">
-        <v>0</v>
-      </c>
-      <c r="R24">
-        <v>13429377.21872473</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18">
-      <c r="A25">
-        <v>3</v>
-      </c>
-      <c r="B25" t="s">
-        <v>125</v>
-      </c>
-      <c r="C25" t="s">
-        <v>253</v>
-      </c>
-      <c r="D25" t="s">
-        <v>228</v>
-      </c>
-      <c r="E25" t="s">
-        <v>268</v>
-      </c>
-      <c r="F25">
-        <v>375.0000000000001</v>
-      </c>
-      <c r="G25">
-        <v>233.014125</v>
-      </c>
-      <c r="H25">
-        <v>1.175471051010843</v>
-      </c>
-      <c r="I25">
-        <v>43.6844274056217</v>
-      </c>
-      <c r="J25">
-        <v>4.570561121208711</v>
-      </c>
-      <c r="K25">
-        <v>6129.213874763306</v>
-      </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="M25">
-        <v>4.570561121208711</v>
-      </c>
-      <c r="N25">
-        <v>0.78</v>
-      </c>
-      <c r="O25">
-        <v>0.357</v>
-      </c>
-      <c r="P25">
-        <v>13373080.86214064</v>
-      </c>
-      <c r="Q25">
-        <v>0</v>
-      </c>
-      <c r="R25">
-        <v>13373080.86214064</v>
+        <v>13004608.44899116</v>
       </c>
     </row>
   </sheetData>
@@ -6497,20 +6214,20 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B70"/>
+  <dimension ref="A1:B60"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="2" t="s">
+      <c r="A1" t="s">
         <v>269</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>186</v>
+        <v>158</v>
       </c>
       <c r="B2">
         <v>4719848.27318464</v>
@@ -6518,143 +6235,143 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>230</v>
+        <v>159</v>
       </c>
       <c r="B3">
-        <v>4215363.528785638</v>
+        <v>4153318.623558146</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>187</v>
+        <v>162</v>
       </c>
       <c r="B4">
-        <v>4719848.27318464</v>
+        <v>3960095.808721507</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>188</v>
+        <v>164</v>
       </c>
       <c r="B5">
-        <v>4651355.367264377</v>
+        <v>4719848.27318464</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>231</v>
+        <v>165</v>
       </c>
       <c r="B6">
-        <v>4217106.914927895</v>
+        <v>4340123.800010766</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>189</v>
+        <v>167</v>
       </c>
       <c r="B7">
-        <v>4719848.27318464</v>
+        <v>3964249.023480296</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>190</v>
+        <v>169</v>
       </c>
       <c r="B8">
-        <v>4582296.713969789</v>
+        <v>4719848.27318464</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>232</v>
+        <v>170</v>
       </c>
       <c r="B9">
-        <v>4218842.598709397</v>
+        <v>4517629.51757387</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>191</v>
+        <v>172</v>
       </c>
       <c r="B10">
-        <v>4719848.27318464</v>
+        <v>3968352.11991846</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="B11">
-        <v>4512641.904149927</v>
+        <v>4719848.27318464</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>233</v>
+        <v>175</v>
       </c>
       <c r="B12">
-        <v>4220568.35887037</v>
+        <v>4620320.376724417</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="B13">
-        <v>4719848.27318464</v>
+        <v>3972405.119967355</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="B14">
-        <v>4370233.447551202</v>
+        <v>4719848.27318464</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>234</v>
+        <v>180</v>
       </c>
       <c r="B15">
-        <v>4222284.9006737</v>
+        <v>4056742.542626799</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="B16">
-        <v>4719848.27318464</v>
+        <v>4033949.605008089</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>235</v>
+        <v>184</v>
       </c>
       <c r="B17">
-        <v>4223994.499606662</v>
+        <v>4719848.27318464</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="B18">
-        <v>4719848.27318464</v>
+        <v>4082487.92356313</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>236</v>
+        <v>187</v>
       </c>
       <c r="B19">
-        <v>4218886.028599959</v>
+        <v>4051491.156438908</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="B20">
         <v>4719848.27318464</v>
@@ -6662,23 +6379,23 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="B21">
-        <v>4559825.285667413</v>
+        <v>4296588.012048371</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>237</v>
+        <v>192</v>
       </c>
       <c r="B22">
-        <v>4220602.97408973</v>
+        <v>4264784.98292635</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="B23">
         <v>4719848.27318464</v>
@@ -6686,23 +6403,23 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="B24">
-        <v>4395076.944624769</v>
+        <v>4300284.718696806</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>238</v>
+        <v>197</v>
       </c>
       <c r="B25">
-        <v>4277208.149063417</v>
+        <v>4266152.899723101</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B26">
         <v>4719848.27318464</v>
@@ -6710,10 +6427,10 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>239</v>
+        <v>200</v>
       </c>
       <c r="B27">
-        <v>4385310.742065813</v>
+        <v>4303956.820596868</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -6721,76 +6438,76 @@
         <v>202</v>
       </c>
       <c r="B28">
-        <v>4719848.27318464</v>
+        <v>4267512.091864506</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B29">
-        <v>4709102.743059322</v>
+        <v>4719848.27318464</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>240</v>
+        <v>205</v>
       </c>
       <c r="B30">
-        <v>4386051.382265373</v>
+        <v>4293116.39393353</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B31">
-        <v>4719848.27318464</v>
+        <v>4268862.652426816</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B32">
-        <v>4589100.989462513</v>
+        <v>4719848.27318464</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>241</v>
+        <v>210</v>
       </c>
       <c r="B33">
-        <v>4386785.729119765</v>
+        <v>4282310.285287289</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="B34">
-        <v>4719848.27318464</v>
+        <v>4270204.660352265</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="B35">
-        <v>4466409.140953656</v>
+        <v>4719848.27318464</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>242</v>
+        <v>215</v>
       </c>
       <c r="B36">
-        <v>4387522.113075241</v>
+        <v>4271538.199802791</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="B37">
         <v>4719848.27318464</v>
@@ -6798,39 +6515,39 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>243</v>
+        <v>218</v>
       </c>
       <c r="B38">
-        <v>4388255.072674902</v>
+        <v>4260799.845747569</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="B39">
-        <v>4719848.27318464</v>
+        <v>4012102.65652155</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="B40">
-        <v>4662190.564484201</v>
+        <v>4719848.27318464</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>244</v>
+        <v>223</v>
       </c>
       <c r="B41">
-        <v>4388980.181271587</v>
+        <v>4497112.975992722</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="B42">
         <v>4719848.27318464</v>
@@ -6838,226 +6555,146 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="B43">
-        <v>4528061.075637412</v>
+        <v>4015643.836980905</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>245</v>
+        <v>228</v>
       </c>
       <c r="B44">
-        <v>4389703.346438444</v>
+        <v>4265228.172845608</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
       <c r="B45">
-        <v>4719848.27318464</v>
+        <v>4019144.629775605</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="B46">
-        <v>4390427.943066845</v>
+        <v>4719848.27318464</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>214</v>
+        <v>233</v>
       </c>
       <c r="B47">
-        <v>4719848.27318464</v>
+        <v>4499192.658911228</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="B48">
-        <v>4248945.751403102</v>
+        <v>4022608.431624907</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="B49">
-        <v>3992706.601016642</v>
+        <v>4719848.27318464</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>216</v>
+        <v>238</v>
       </c>
       <c r="B50">
-        <v>4719848.27318464</v>
+        <v>4269563.337796072</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="B51">
-        <v>4491720.654554019</v>
+        <v>4026033.715253451</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="B52">
-        <v>3996585.168007816</v>
+        <v>4719848.27318464</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>218</v>
+        <v>243</v>
       </c>
       <c r="B53">
-        <v>4719848.27318464</v>
+        <v>4501229.973452239</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>219</v>
+        <v>247</v>
       </c>
       <c r="B54">
-        <v>4253773.090416066</v>
+        <v>4719848.27318464</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="B55">
-        <v>4000409.836050834</v>
+        <v>4029422.796164739</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>220</v>
+        <v>248</v>
       </c>
       <c r="B56">
-        <v>4719848.27318464</v>
+        <v>4273808.429490295</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>221</v>
+        <v>250</v>
       </c>
       <c r="B57">
-        <v>4493979.833443145</v>
+        <v>4032775.141727288</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B58">
-        <v>4004197.098644243</v>
+        <v>4719848.27318464</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>222</v>
+        <v>253</v>
       </c>
       <c r="B59">
-        <v>4719848.27318464</v>
+        <v>4503226.28198659</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>223</v>
+        <v>255</v>
       </c>
       <c r="B60">
-        <v>4258491.258129958</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2">
-      <c r="A61" t="s">
-        <v>251</v>
-      </c>
-      <c r="B61">
-        <v>4007932.971744596</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2">
-      <c r="A62" t="s">
-        <v>224</v>
-      </c>
-      <c r="B62">
-        <v>4719848.27318464</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2">
-      <c r="A63" t="s">
-        <v>225</v>
-      </c>
-      <c r="B63">
-        <v>4496189.582882936</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2">
-      <c r="A64" t="s">
-        <v>252</v>
-      </c>
-      <c r="B64">
-        <v>4011632.208642931</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2">
-      <c r="A65" t="s">
-        <v>226</v>
-      </c>
-      <c r="B65">
-        <v>4719848.27318464</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2">
-      <c r="A66" t="s">
-        <v>227</v>
-      </c>
-      <c r="B66">
-        <v>4263104.021114981</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2">
-      <c r="A67" t="s">
-        <v>253</v>
-      </c>
-      <c r="B67">
-        <v>4015282.442834999</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2">
-      <c r="A68" t="s">
-        <v>228</v>
-      </c>
-      <c r="B68">
-        <v>4719848.27318464</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2">
-      <c r="A69" t="s">
-        <v>229</v>
-      </c>
-      <c r="B69">
-        <v>4498351.552590257</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2">
-      <c r="A70" t="s">
-        <v>254</v>
-      </c>
-      <c r="B70">
-        <v>4018896.773959124</v>
+        <v>4036092.034052541</v>
       </c>
     </row>
   </sheetData>
@@ -7071,37 +6708,37 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="2" t="s">
+      <c r="A1" t="s">
         <v>271</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
         <v>272</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" t="s">
         <v>273</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" t="s">
         <v>274</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" t="s">
         <v>275</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" t="s">
         <v>276</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="B2">
         <v>17.65832997587177</v>
       </c>
       <c r="C2">
-        <v>17.65832997587171</v>
+        <v>17.65832997586855</v>
       </c>
       <c r="D2">
         <v>65.15454188318284</v>
@@ -7110,15 +6747,15 @@
         <v>1150.5204</v>
       </c>
       <c r="F2">
-        <v>1150.520399999996</v>
+        <v>1150.520399999791</v>
       </c>
       <c r="G2">
-        <v>-3.219071052499218E-13</v>
+        <v>-1.818775144662058E-11</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B3">
         <v>45.91165732334162</v>
@@ -7160,6 +6797,839 @@
       </c>
       <c r="G4">
         <v>4.023838815624023E-14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I50"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
+        <v>281</v>
+      </c>
+      <c r="B2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>283</v>
+      </c>
+      <c r="B3" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>285</v>
+      </c>
+      <c r="B4" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>287</v>
+      </c>
+      <c r="B5" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>289</v>
+      </c>
+      <c r="B6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
+        <v>291</v>
+      </c>
+      <c r="B7" t="s">
+        <v>292</v>
+      </c>
+      <c r="C7" t="s">
+        <v>293</v>
+      </c>
+      <c r="D7" t="s">
+        <v>294</v>
+      </c>
+      <c r="E7" t="s">
+        <v>293</v>
+      </c>
+      <c r="F7" t="s">
+        <v>295</v>
+      </c>
+      <c r="G7" t="s">
+        <v>293</v>
+      </c>
+      <c r="H7" t="s">
+        <v>296</v>
+      </c>
+      <c r="I7" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" t="s">
+        <v>297</v>
+      </c>
+      <c r="B8" t="s">
+        <v>298</v>
+      </c>
+      <c r="C8" t="s">
+        <v>299</v>
+      </c>
+      <c r="D8" t="s">
+        <v>300</v>
+      </c>
+      <c r="E8" t="s">
+        <v>301</v>
+      </c>
+      <c r="F8" t="s">
+        <v>302</v>
+      </c>
+      <c r="G8" t="s">
+        <v>303</v>
+      </c>
+      <c r="H8" t="s">
+        <v>304</v>
+      </c>
+      <c r="I8" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" t="s">
+        <v>306</v>
+      </c>
+      <c r="B9" t="s">
+        <v>307</v>
+      </c>
+      <c r="C9" t="s">
+        <v>293</v>
+      </c>
+      <c r="D9" t="s">
+        <v>294</v>
+      </c>
+      <c r="E9" t="s">
+        <v>293</v>
+      </c>
+      <c r="F9" t="s">
+        <v>296</v>
+      </c>
+      <c r="G9" t="s">
+        <v>284</v>
+      </c>
+      <c r="H9" t="s">
+        <v>308</v>
+      </c>
+      <c r="I9" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" t="s">
+        <v>310</v>
+      </c>
+      <c r="B10" t="s">
+        <v>307</v>
+      </c>
+      <c r="C10" t="s">
+        <v>293</v>
+      </c>
+      <c r="D10" t="s">
+        <v>304</v>
+      </c>
+      <c r="E10" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" t="s">
+        <v>311</v>
+      </c>
+      <c r="B11" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" t="s">
+        <v>312</v>
+      </c>
+      <c r="B12" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" t="s">
+        <v>313</v>
+      </c>
+      <c r="B13" t="s">
+        <v>307</v>
+      </c>
+      <c r="C13" t="s">
+        <v>293</v>
+      </c>
+      <c r="D13" t="s">
+        <v>304</v>
+      </c>
+      <c r="E13" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" t="s">
+        <v>314</v>
+      </c>
+      <c r="B14" t="s">
+        <v>307</v>
+      </c>
+      <c r="C14" t="s">
+        <v>293</v>
+      </c>
+      <c r="D14" t="s">
+        <v>315</v>
+      </c>
+      <c r="E14" t="s">
+        <v>293</v>
+      </c>
+      <c r="F14" t="s">
+        <v>304</v>
+      </c>
+      <c r="G14" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" t="s">
+        <v>316</v>
+      </c>
+      <c r="B15" t="s">
+        <v>307</v>
+      </c>
+      <c r="C15" t="s">
+        <v>293</v>
+      </c>
+      <c r="D15" t="s">
+        <v>304</v>
+      </c>
+      <c r="E15" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" t="s">
+        <v>317</v>
+      </c>
+      <c r="B16" t="s">
+        <v>307</v>
+      </c>
+      <c r="C16" t="s">
+        <v>293</v>
+      </c>
+      <c r="D16" t="s">
+        <v>304</v>
+      </c>
+      <c r="E16" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" t="s">
+        <v>318</v>
+      </c>
+      <c r="B17" t="s">
+        <v>307</v>
+      </c>
+      <c r="C17" t="s">
+        <v>293</v>
+      </c>
+      <c r="D17" t="s">
+        <v>304</v>
+      </c>
+      <c r="E17" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" t="s">
+        <v>319</v>
+      </c>
+      <c r="B18" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" t="s">
+        <v>320</v>
+      </c>
+      <c r="B19" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" t="s">
+        <v>321</v>
+      </c>
+      <c r="B20" t="s">
+        <v>307</v>
+      </c>
+      <c r="C20" t="s">
+        <v>293</v>
+      </c>
+      <c r="D20" t="s">
+        <v>322</v>
+      </c>
+      <c r="E20" t="s">
+        <v>323</v>
+      </c>
+      <c r="F20" t="s">
+        <v>324</v>
+      </c>
+      <c r="G20" t="s">
+        <v>325</v>
+      </c>
+      <c r="H20" t="s">
+        <v>326</v>
+      </c>
+      <c r="I20" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" t="s">
+        <v>327</v>
+      </c>
+      <c r="B21" t="s">
+        <v>307</v>
+      </c>
+      <c r="C21" t="s">
+        <v>293</v>
+      </c>
+      <c r="D21" t="s">
+        <v>322</v>
+      </c>
+      <c r="E21" t="s">
+        <v>328</v>
+      </c>
+      <c r="F21" t="s">
+        <v>324</v>
+      </c>
+      <c r="G21" t="s">
+        <v>325</v>
+      </c>
+      <c r="H21" t="s">
+        <v>326</v>
+      </c>
+      <c r="I21" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" t="s">
+        <v>329</v>
+      </c>
+      <c r="B22" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" t="s">
+        <v>331</v>
+      </c>
+      <c r="B23" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" t="s">
+        <v>333</v>
+      </c>
+      <c r="B24" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" t="s">
+        <v>334</v>
+      </c>
+      <c r="B25" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" t="s">
+        <v>336</v>
+      </c>
+      <c r="B26" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" t="s">
+        <v>337</v>
+      </c>
+      <c r="B27" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" t="s">
+        <v>338</v>
+      </c>
+      <c r="B28" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" t="s">
+        <v>339</v>
+      </c>
+      <c r="B29" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" t="s">
+        <v>341</v>
+      </c>
+      <c r="B30" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" t="s">
+        <v>343</v>
+      </c>
+      <c r="B31" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" t="s">
+        <v>345</v>
+      </c>
+      <c r="B32" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" t="s">
+        <v>347</v>
+      </c>
+      <c r="B33" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" t="s">
+        <v>348</v>
+      </c>
+      <c r="B34" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" t="s">
+        <v>349</v>
+      </c>
+      <c r="B35" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" t="s">
+        <v>351</v>
+      </c>
+      <c r="B36" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" t="s">
+        <v>353</v>
+      </c>
+      <c r="B37" t="s">
+        <v>354</v>
+      </c>
+      <c r="C37" t="s">
+        <v>284</v>
+      </c>
+      <c r="D37" t="s">
+        <v>355</v>
+      </c>
+      <c r="E37" t="s">
+        <v>323</v>
+      </c>
+      <c r="F37" t="s">
+        <v>356</v>
+      </c>
+      <c r="G37" t="s">
+        <v>288</v>
+      </c>
+      <c r="H37" t="s">
+        <v>357</v>
+      </c>
+      <c r="I37" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" t="s">
+        <v>359</v>
+      </c>
+      <c r="B38" t="s">
+        <v>354</v>
+      </c>
+      <c r="C38" t="s">
+        <v>360</v>
+      </c>
+      <c r="D38" t="s">
+        <v>355</v>
+      </c>
+      <c r="E38" t="s">
+        <v>323</v>
+      </c>
+      <c r="F38" t="s">
+        <v>356</v>
+      </c>
+      <c r="G38" t="s">
+        <v>288</v>
+      </c>
+      <c r="H38" t="s">
+        <v>357</v>
+      </c>
+      <c r="I38" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" t="s">
+        <v>361</v>
+      </c>
+      <c r="B39" t="s">
+        <v>354</v>
+      </c>
+      <c r="C39" t="s">
+        <v>362</v>
+      </c>
+      <c r="D39" t="s">
+        <v>355</v>
+      </c>
+      <c r="E39" t="s">
+        <v>323</v>
+      </c>
+      <c r="F39" t="s">
+        <v>356</v>
+      </c>
+      <c r="G39" t="s">
+        <v>288</v>
+      </c>
+      <c r="H39" t="s">
+        <v>357</v>
+      </c>
+      <c r="I39" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" t="s">
+        <v>363</v>
+      </c>
+      <c r="B40" t="s">
+        <v>354</v>
+      </c>
+      <c r="C40" t="s">
+        <v>284</v>
+      </c>
+      <c r="D40" t="s">
+        <v>355</v>
+      </c>
+      <c r="E40" t="s">
+        <v>323</v>
+      </c>
+      <c r="F40" t="s">
+        <v>356</v>
+      </c>
+      <c r="G40" t="s">
+        <v>288</v>
+      </c>
+      <c r="H40" t="s">
+        <v>357</v>
+      </c>
+      <c r="I40" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" t="s">
+        <v>364</v>
+      </c>
+      <c r="B41" t="s">
+        <v>354</v>
+      </c>
+      <c r="C41" t="s">
+        <v>365</v>
+      </c>
+      <c r="D41" t="s">
+        <v>355</v>
+      </c>
+      <c r="E41" t="s">
+        <v>323</v>
+      </c>
+      <c r="F41" t="s">
+        <v>356</v>
+      </c>
+      <c r="G41" t="s">
+        <v>288</v>
+      </c>
+      <c r="H41" t="s">
+        <v>357</v>
+      </c>
+      <c r="I41" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" t="s">
+        <v>366</v>
+      </c>
+      <c r="B42" t="s">
+        <v>354</v>
+      </c>
+      <c r="C42" t="s">
+        <v>367</v>
+      </c>
+      <c r="D42" t="s">
+        <v>355</v>
+      </c>
+      <c r="E42" t="s">
+        <v>323</v>
+      </c>
+      <c r="F42" t="s">
+        <v>356</v>
+      </c>
+      <c r="G42" t="s">
+        <v>288</v>
+      </c>
+      <c r="H42" t="s">
+        <v>357</v>
+      </c>
+      <c r="I42" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43" t="s">
+        <v>368</v>
+      </c>
+      <c r="B43" t="s">
+        <v>354</v>
+      </c>
+      <c r="C43" t="s">
+        <v>293</v>
+      </c>
+      <c r="D43" t="s">
+        <v>355</v>
+      </c>
+      <c r="E43" t="s">
+        <v>323</v>
+      </c>
+      <c r="F43" t="s">
+        <v>356</v>
+      </c>
+      <c r="G43" t="s">
+        <v>288</v>
+      </c>
+      <c r="H43" t="s">
+        <v>357</v>
+      </c>
+      <c r="I43" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44" t="s">
+        <v>91</v>
+      </c>
+      <c r="B44" t="s">
+        <v>354</v>
+      </c>
+      <c r="C44" t="s">
+        <v>284</v>
+      </c>
+      <c r="D44" t="s">
+        <v>355</v>
+      </c>
+      <c r="E44" t="s">
+        <v>323</v>
+      </c>
+      <c r="F44" t="s">
+        <v>356</v>
+      </c>
+      <c r="G44" t="s">
+        <v>288</v>
+      </c>
+      <c r="H44" t="s">
+        <v>357</v>
+      </c>
+      <c r="I44" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45" t="s">
+        <v>369</v>
+      </c>
+      <c r="B45" t="s">
+        <v>354</v>
+      </c>
+      <c r="C45" t="s">
+        <v>284</v>
+      </c>
+      <c r="D45" t="s">
+        <v>355</v>
+      </c>
+      <c r="E45" t="s">
+        <v>323</v>
+      </c>
+      <c r="F45" t="s">
+        <v>356</v>
+      </c>
+      <c r="G45" t="s">
+        <v>288</v>
+      </c>
+      <c r="H45" t="s">
+        <v>357</v>
+      </c>
+      <c r="I45" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46" t="s">
+        <v>370</v>
+      </c>
+      <c r="B46" t="s">
+        <v>354</v>
+      </c>
+      <c r="C46" t="s">
+        <v>371</v>
+      </c>
+      <c r="D46" t="s">
+        <v>372</v>
+      </c>
+      <c r="E46" t="s">
+        <v>373</v>
+      </c>
+      <c r="F46" t="s">
+        <v>304</v>
+      </c>
+      <c r="G46" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47" t="s">
+        <v>374</v>
+      </c>
+      <c r="B47" t="s">
+        <v>354</v>
+      </c>
+      <c r="C47" t="s">
+        <v>342</v>
+      </c>
+      <c r="D47" t="s">
+        <v>372</v>
+      </c>
+      <c r="E47" t="s">
+        <v>293</v>
+      </c>
+      <c r="F47" t="s">
+        <v>304</v>
+      </c>
+      <c r="G47" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48" t="s">
+        <v>375</v>
+      </c>
+      <c r="B48" t="s">
+        <v>354</v>
+      </c>
+      <c r="C48" t="s">
+        <v>342</v>
+      </c>
+      <c r="D48" t="s">
+        <v>372</v>
+      </c>
+      <c r="E48" t="s">
+        <v>293</v>
+      </c>
+      <c r="F48" t="s">
+        <v>304</v>
+      </c>
+      <c r="G48" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" t="s">
+        <v>376</v>
+      </c>
+      <c r="B49" t="s">
+        <v>354</v>
+      </c>
+      <c r="C49" t="s">
+        <v>371</v>
+      </c>
+      <c r="D49" t="s">
+        <v>372</v>
+      </c>
+      <c r="E49" t="s">
+        <v>293</v>
+      </c>
+      <c r="F49" t="s">
+        <v>304</v>
+      </c>
+      <c r="G49" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" t="s">
+        <v>377</v>
+      </c>
+      <c r="B50" t="s">
+        <v>354</v>
+      </c>
+      <c r="C50" t="s">
+        <v>378</v>
+      </c>
+      <c r="D50" t="s">
+        <v>304</v>
+      </c>
+      <c r="E50" t="s">
+        <v>305</v>
       </c>
     </row>
   </sheetData>
